--- a/life_table_tidy.xlsx
+++ b/life_table_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9503D1CD-B29F-4E55-B5DD-D7E1728F4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{9503D1CD-B29F-4E55-B5DD-D7E1728F4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F12CFB2-B459-449B-AE79-7692FA663B90}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{43AF6025-F2CC-4099-8FD0-C1C779A276C3}"/>
+    <workbookView xWindow="0" yWindow="1764" windowWidth="17280" windowHeight="8880" xr2:uid="{43AF6025-F2CC-4099-8FD0-C1C779A276C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="10">
   <si>
     <t>Age</t>
   </si>
@@ -149,6 +149,12 @@
   <si>
     <t>Female</t>
   </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
 </sst>
 </file>
 
@@ -156,10 +162,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +210,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -227,14 +240,14 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -242,6 +255,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -558,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF1BE32-6C5E-4AA8-8DE0-B4C2A43B98B9}">
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -569,7 +583,7 @@
     <col min="6" max="6" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -588,8 +602,11 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -608,8 +625,11 @@
       <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -628,8 +648,11 @@
       <c r="F3" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -648,8 +671,11 @@
       <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -668,8 +694,11 @@
       <c r="F5" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -688,8 +717,11 @@
       <c r="F6" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -708,8 +740,11 @@
       <c r="F7" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -728,8 +763,11 @@
       <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -748,8 +786,11 @@
       <c r="F9" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -768,8 +809,11 @@
       <c r="F10" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -788,8 +832,11 @@
       <c r="F11" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -808,8 +855,11 @@
       <c r="F12" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -828,8 +878,11 @@
       <c r="F13" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -848,8 +901,11 @@
       <c r="F14" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -868,8 +924,11 @@
       <c r="F15" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -888,8 +947,11 @@
       <c r="F16" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -908,8 +970,11 @@
       <c r="F17" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -928,8 +993,11 @@
       <c r="F18" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -948,8 +1016,11 @@
       <c r="F19" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -968,8 +1039,11 @@
       <c r="F20" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -988,8 +1062,11 @@
       <c r="F21" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1008,8 +1085,11 @@
       <c r="F22" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1028,8 +1108,11 @@
       <c r="F23" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1048,8 +1131,11 @@
       <c r="F24" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1068,8 +1154,11 @@
       <c r="F25" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1088,8 +1177,11 @@
       <c r="F26" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1108,8 +1200,11 @@
       <c r="F27" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1128,8 +1223,11 @@
       <c r="F28" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1148,8 +1246,11 @@
       <c r="F29" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1168,8 +1269,11 @@
       <c r="F30" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1188,8 +1292,11 @@
       <c r="F31" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1208,8 +1315,11 @@
       <c r="F32" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1228,8 +1338,11 @@
       <c r="F33" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1248,8 +1361,11 @@
       <c r="F34" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -1268,8 +1384,11 @@
       <c r="F35" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -1288,8 +1407,11 @@
       <c r="F36" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1308,8 +1430,11 @@
       <c r="F37" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -1328,8 +1453,11 @@
       <c r="F38" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -1348,8 +1476,11 @@
       <c r="F39" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -1368,8 +1499,11 @@
       <c r="F40" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -1388,8 +1522,11 @@
       <c r="F41" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -1408,8 +1545,11 @@
       <c r="F42" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -1428,8 +1568,11 @@
       <c r="F43" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -1448,8 +1591,11 @@
       <c r="F44" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -1468,8 +1614,11 @@
       <c r="F45" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -1488,8 +1637,11 @@
       <c r="F46" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -1508,8 +1660,11 @@
       <c r="F47" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -1528,8 +1683,11 @@
       <c r="F48" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -1548,8 +1706,11 @@
       <c r="F49" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -1568,8 +1729,11 @@
       <c r="F50" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -1588,8 +1752,11 @@
       <c r="F51" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -1608,8 +1775,11 @@
       <c r="F52" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G52" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -1628,8 +1798,11 @@
       <c r="F53" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G53" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -1648,8 +1821,11 @@
       <c r="F54" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G54" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1668,8 +1844,11 @@
       <c r="F55" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -1688,8 +1867,11 @@
       <c r="F56" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -1708,8 +1890,11 @@
       <c r="F57" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -1728,8 +1913,11 @@
       <c r="F58" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G58" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -1748,8 +1936,11 @@
       <c r="F59" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -1768,8 +1959,11 @@
       <c r="F60" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -1788,8 +1982,11 @@
       <c r="F61" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G61" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -1808,8 +2005,11 @@
       <c r="F62" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G62" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -1828,8 +2028,11 @@
       <c r="F63" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G63" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -1848,8 +2051,11 @@
       <c r="F64" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -1868,8 +2074,11 @@
       <c r="F65" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -1888,8 +2097,11 @@
       <c r="F66" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -1908,8 +2120,11 @@
       <c r="F67" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G67" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -1928,8 +2143,11 @@
       <c r="F68" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G68" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -1948,8 +2166,11 @@
       <c r="F69" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -1968,8 +2189,11 @@
       <c r="F70" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G70" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -1988,8 +2212,11 @@
       <c r="F71" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G71" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -2008,8 +2235,11 @@
       <c r="F72" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -2028,8 +2258,11 @@
       <c r="F73" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G73" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -2048,8 +2281,11 @@
       <c r="F74" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -2068,8 +2304,11 @@
       <c r="F75" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -2088,8 +2327,11 @@
       <c r="F76" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G76" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -2108,8 +2350,11 @@
       <c r="F77" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G77" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -2128,8 +2373,11 @@
       <c r="F78" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G78" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -2148,8 +2396,11 @@
       <c r="F79" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G79" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -2168,8 +2419,11 @@
       <c r="F80" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G80" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -2188,8 +2442,11 @@
       <c r="F81" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -2208,8 +2465,11 @@
       <c r="F82" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -2228,8 +2488,11 @@
       <c r="F83" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -2248,8 +2511,11 @@
       <c r="F84" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -2268,8 +2534,11 @@
       <c r="F85" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -2288,8 +2557,11 @@
       <c r="F86" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -2308,8 +2580,11 @@
       <c r="F87" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -2328,8 +2603,11 @@
       <c r="F88" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -2348,8 +2626,11 @@
       <c r="F89" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -2368,8 +2649,11 @@
       <c r="F90" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -2388,8 +2672,11 @@
       <c r="F91" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G91" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -2408,8 +2695,11 @@
       <c r="F92" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -2428,8 +2718,11 @@
       <c r="F93" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G93" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -2448,8 +2741,11 @@
       <c r="F94" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G94" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -2468,8 +2764,11 @@
       <c r="F95" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G95" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -2488,8 +2787,11 @@
       <c r="F96" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G96" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -2508,8 +2810,11 @@
       <c r="F97" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G97" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -2528,8 +2833,11 @@
       <c r="F98" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -2548,8 +2856,11 @@
       <c r="F99" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G99" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -2568,8 +2879,11 @@
       <c r="F100" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G100" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -2588,8 +2902,11 @@
       <c r="F101" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G101" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -2608,8 +2925,11 @@
       <c r="F102" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G102" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>0</v>
       </c>
@@ -2628,8 +2948,11 @@
       <c r="F103" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G103" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>1</v>
       </c>
@@ -2648,8 +2971,11 @@
       <c r="F104" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G104" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>2</v>
       </c>
@@ -2668,8 +2994,11 @@
       <c r="F105" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G105" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>3</v>
       </c>
@@ -2688,8 +3017,11 @@
       <c r="F106" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G106" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>4</v>
       </c>
@@ -2708,8 +3040,11 @@
       <c r="F107" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G107" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>5</v>
       </c>
@@ -2728,8 +3063,11 @@
       <c r="F108" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G108" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>6</v>
       </c>
@@ -2748,8 +3086,11 @@
       <c r="F109" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G109" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>7</v>
       </c>
@@ -2768,8 +3109,11 @@
       <c r="F110" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G110" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>8</v>
       </c>
@@ -2788,8 +3132,11 @@
       <c r="F111" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G111" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>9</v>
       </c>
@@ -2808,8 +3155,11 @@
       <c r="F112" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G112" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>10</v>
       </c>
@@ -2828,8 +3178,11 @@
       <c r="F113" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G113" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>11</v>
       </c>
@@ -2848,8 +3201,11 @@
       <c r="F114" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G114" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>12</v>
       </c>
@@ -2868,8 +3224,11 @@
       <c r="F115" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G115" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>13</v>
       </c>
@@ -2888,8 +3247,11 @@
       <c r="F116" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G116" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>14</v>
       </c>
@@ -2908,8 +3270,11 @@
       <c r="F117" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G117" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>15</v>
       </c>
@@ -2928,8 +3293,11 @@
       <c r="F118" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G118" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>16</v>
       </c>
@@ -2948,8 +3316,11 @@
       <c r="F119" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G119" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>17</v>
       </c>
@@ -2968,8 +3339,11 @@
       <c r="F120" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G120" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>18</v>
       </c>
@@ -2988,8 +3362,11 @@
       <c r="F121" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>19</v>
       </c>
@@ -3008,8 +3385,11 @@
       <c r="F122" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G122" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>20</v>
       </c>
@@ -3028,8 +3408,11 @@
       <c r="F123" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G123" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>21</v>
       </c>
@@ -3048,8 +3431,11 @@
       <c r="F124" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G124" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>22</v>
       </c>
@@ -3068,8 +3454,11 @@
       <c r="F125" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G125" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>23</v>
       </c>
@@ -3088,8 +3477,11 @@
       <c r="F126" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G126" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>24</v>
       </c>
@@ -3108,8 +3500,11 @@
       <c r="F127" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G127" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>25</v>
       </c>
@@ -3128,8 +3523,11 @@
       <c r="F128" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G128" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>26</v>
       </c>
@@ -3148,8 +3546,11 @@
       <c r="F129" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G129" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>27</v>
       </c>
@@ -3168,8 +3569,11 @@
       <c r="F130" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G130" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>28</v>
       </c>
@@ -3188,8 +3592,11 @@
       <c r="F131" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G131" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>29</v>
       </c>
@@ -3208,8 +3615,11 @@
       <c r="F132" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G132" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>30</v>
       </c>
@@ -3228,8 +3638,11 @@
       <c r="F133" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G133" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>31</v>
       </c>
@@ -3248,8 +3661,11 @@
       <c r="F134" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G134" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>32</v>
       </c>
@@ -3268,8 +3684,11 @@
       <c r="F135" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G135" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>33</v>
       </c>
@@ -3288,8 +3707,11 @@
       <c r="F136" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G136" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>34</v>
       </c>
@@ -3308,8 +3730,11 @@
       <c r="F137" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G137" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>35</v>
       </c>
@@ -3328,8 +3753,11 @@
       <c r="F138" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G138" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>36</v>
       </c>
@@ -3348,8 +3776,11 @@
       <c r="F139" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G139" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>37</v>
       </c>
@@ -3368,8 +3799,11 @@
       <c r="F140" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G140" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>38</v>
       </c>
@@ -3388,8 +3822,11 @@
       <c r="F141" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G141" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>39</v>
       </c>
@@ -3408,8 +3845,11 @@
       <c r="F142" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G142" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>40</v>
       </c>
@@ -3428,8 +3868,11 @@
       <c r="F143" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G143" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>41</v>
       </c>
@@ -3448,8 +3891,11 @@
       <c r="F144" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G144" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>42</v>
       </c>
@@ -3468,8 +3914,11 @@
       <c r="F145" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G145" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>43</v>
       </c>
@@ -3488,8 +3937,11 @@
       <c r="F146" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G146" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>44</v>
       </c>
@@ -3508,8 +3960,11 @@
       <c r="F147" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G147" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45</v>
       </c>
@@ -3528,8 +3983,11 @@
       <c r="F148" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G148" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46</v>
       </c>
@@ -3548,8 +4006,11 @@
       <c r="F149" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G149" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>47</v>
       </c>
@@ -3568,8 +4029,11 @@
       <c r="F150" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G150" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>48</v>
       </c>
@@ -3588,8 +4052,11 @@
       <c r="F151" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G151" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>49</v>
       </c>
@@ -3608,8 +4075,11 @@
       <c r="F152" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G152" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>50</v>
       </c>
@@ -3628,8 +4098,11 @@
       <c r="F153" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G153" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>51</v>
       </c>
@@ -3648,8 +4121,11 @@
       <c r="F154" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G154" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>52</v>
       </c>
@@ -3668,8 +4144,11 @@
       <c r="F155" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G155" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>53</v>
       </c>
@@ -3688,8 +4167,11 @@
       <c r="F156" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G156" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>54</v>
       </c>
@@ -3708,8 +4190,11 @@
       <c r="F157" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G157" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>55</v>
       </c>
@@ -3728,8 +4213,11 @@
       <c r="F158" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G158" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>56</v>
       </c>
@@ -3748,8 +4236,11 @@
       <c r="F159" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G159" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>57</v>
       </c>
@@ -3768,8 +4259,11 @@
       <c r="F160" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G160" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>58</v>
       </c>
@@ -3788,8 +4282,11 @@
       <c r="F161" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G161" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>59</v>
       </c>
@@ -3808,8 +4305,11 @@
       <c r="F162" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G162" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>60</v>
       </c>
@@ -3828,8 +4328,11 @@
       <c r="F163" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G163" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>61</v>
       </c>
@@ -3848,8 +4351,11 @@
       <c r="F164" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G164" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>62</v>
       </c>
@@ -3868,8 +4374,11 @@
       <c r="F165" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G165" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>63</v>
       </c>
@@ -3888,8 +4397,11 @@
       <c r="F166" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G166" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>64</v>
       </c>
@@ -3908,8 +4420,11 @@
       <c r="F167" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G167" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>65</v>
       </c>
@@ -3928,8 +4443,11 @@
       <c r="F168" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G168" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>66</v>
       </c>
@@ -3948,8 +4466,11 @@
       <c r="F169" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G169" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>67</v>
       </c>
@@ -3968,8 +4489,11 @@
       <c r="F170" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G170" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>68</v>
       </c>
@@ -3988,8 +4512,11 @@
       <c r="F171" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G171" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>69</v>
       </c>
@@ -4008,8 +4535,11 @@
       <c r="F172" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G172" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>70</v>
       </c>
@@ -4028,8 +4558,11 @@
       <c r="F173" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G173" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>71</v>
       </c>
@@ -4048,8 +4581,11 @@
       <c r="F174" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G174" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>72</v>
       </c>
@@ -4068,8 +4604,11 @@
       <c r="F175" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G175" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>73</v>
       </c>
@@ -4088,8 +4627,11 @@
       <c r="F176" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G176" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>74</v>
       </c>
@@ -4108,8 +4650,11 @@
       <c r="F177" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G177" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>75</v>
       </c>
@@ -4128,8 +4673,11 @@
       <c r="F178" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G178" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>76</v>
       </c>
@@ -4148,8 +4696,11 @@
       <c r="F179" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G179" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>77</v>
       </c>
@@ -4168,8 +4719,11 @@
       <c r="F180" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G180" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>78</v>
       </c>
@@ -4188,8 +4742,11 @@
       <c r="F181" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G181" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>79</v>
       </c>
@@ -4208,8 +4765,11 @@
       <c r="F182" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G182" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>80</v>
       </c>
@@ -4228,8 +4788,11 @@
       <c r="F183" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G183" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>81</v>
       </c>
@@ -4248,8 +4811,11 @@
       <c r="F184" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G184" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>82</v>
       </c>
@@ -4268,8 +4834,11 @@
       <c r="F185" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G185" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>83</v>
       </c>
@@ -4288,8 +4857,11 @@
       <c r="F186" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G186" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>84</v>
       </c>
@@ -4308,8 +4880,11 @@
       <c r="F187" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G187" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>85</v>
       </c>
@@ -4328,8 +4903,11 @@
       <c r="F188" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G188" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>86</v>
       </c>
@@ -4348,8 +4926,11 @@
       <c r="F189" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G189" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>87</v>
       </c>
@@ -4368,8 +4949,11 @@
       <c r="F190" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G190" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>88</v>
       </c>
@@ -4388,8 +4972,11 @@
       <c r="F191" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G191" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>89</v>
       </c>
@@ -4408,8 +4995,11 @@
       <c r="F192" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G192" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>90</v>
       </c>
@@ -4428,8 +5018,11 @@
       <c r="F193" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G193" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>91</v>
       </c>
@@ -4448,8 +5041,11 @@
       <c r="F194" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G194" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>92</v>
       </c>
@@ -4468,8 +5064,11 @@
       <c r="F195" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G195" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>93</v>
       </c>
@@ -4488,8 +5087,11 @@
       <c r="F196" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G196" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>94</v>
       </c>
@@ -4508,8 +5110,11 @@
       <c r="F197" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G197" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>95</v>
       </c>
@@ -4528,8 +5133,11 @@
       <c r="F198" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G198" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>96</v>
       </c>
@@ -4548,8 +5156,11 @@
       <c r="F199" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G199" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>97</v>
       </c>
@@ -4568,8 +5179,11 @@
       <c r="F200" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G200" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>98</v>
       </c>
@@ -4588,8 +5202,11 @@
       <c r="F201" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G201" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>99</v>
       </c>
@@ -4608,8 +5225,11 @@
       <c r="F202" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G202" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100</v>
       </c>
@@ -4627,6 +5247,9 @@
       </c>
       <c r="F203" s="7" t="s">
         <v>7</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/life_table_tidy.xlsx
+++ b/life_table_tidy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{9503D1CD-B29F-4E55-B5DD-D7E1728F4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F12CFB2-B459-449B-AE79-7692FA663B90}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{9503D1CD-B29F-4E55-B5DD-D7E1728F4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F0FA82B-D184-40E8-BB84-E2860136FA77}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1764" windowWidth="17280" windowHeight="8880" xr2:uid="{43AF6025-F2CC-4099-8FD0-C1C779A276C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{43AF6025-F2CC-4099-8FD0-C1C779A276C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{791BB92B-E85F-42E7-BFF9-07B045830072}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{791BB92B-E85F-42E7-BFF9-07B045830072}">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{269050B6-6569-48A9-BAE9-AE90D478F7F5}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{269050B6-6569-48A9-BAE9-AE90D478F7F5}">
       <text>
         <r>
           <rPr>
@@ -91,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0" xr:uid="{A64654BF-9E06-4954-BEC5-C2BC664A895F}">
+    <comment ref="G102" authorId="0" shapeId="0" xr:uid="{A64654BF-9E06-4954-BEC5-C2BC664A895F}">
       <text>
         <r>
           <rPr>
@@ -105,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D203" authorId="0" shapeId="0" xr:uid="{8273139F-6947-4DCE-B40D-44FFA34BD8F2}">
+    <comment ref="G203" authorId="0" shapeId="0" xr:uid="{8273139F-6947-4DCE-B40D-44FFA34BD8F2}">
       <text>
         <r>
           <rPr>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="15">
   <si>
     <t>Age</t>
   </si>
@@ -154,6 +154,21 @@
   </si>
   <si>
     <t>Australia</t>
+  </si>
+  <si>
+    <t>px</t>
+  </si>
+  <si>
+    <t>Sx</t>
+  </si>
+  <si>
+    <t>lnqx</t>
+  </si>
+  <si>
+    <t>lnqx = ln(10^6*qx)</t>
+  </si>
+  <si>
+    <t>Sx = S(x)</t>
   </si>
 </sst>
 </file>
@@ -240,7 +255,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -256,6 +271,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -572,18 +588,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF1BE32-6C5E-4AA8-8DE0-B4C2A43B98B9}">
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="7"/>
+    <col min="3" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="7"/>
+    <col min="15" max="15" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -593,20 +610,29 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -616,20 +642,31 @@
       <c r="C2" s="3">
         <v>3.5300000000000002E-3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
+        <f>LN(10^6*C2)</f>
+        <v>8.1690531499273433</v>
+      </c>
+      <c r="E2" s="3">
+        <f>1-C2</f>
+        <v>0.99646999999999997</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
         <v>99681</v>
       </c>
-      <c r="E2" s="3">
+      <c r="H2" s="3">
         <v>81.06156</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -639,20 +676,32 @@
       <c r="C3" s="3">
         <v>2.4000000000000001E-4</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D66" si="0">LN(10^6*C3)</f>
+        <v>5.4806389233419912</v>
+      </c>
+      <c r="E3" s="3">
+        <f>1-C3</f>
+        <v>0.99975999999999998</v>
+      </c>
+      <c r="F3" s="9">
+        <f>PRODUCT(E$2:$E2)</f>
+        <v>0.99646999999999997</v>
+      </c>
+      <c r="G3" s="2">
         <v>99634</v>
       </c>
-      <c r="E3" s="3">
+      <c r="H3" s="3">
         <v>80.348169999999996</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -662,20 +711,32 @@
       <c r="C4" s="3">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" ref="E4:E67" si="1">1-C4</f>
+        <v>0.99985000000000002</v>
+      </c>
+      <c r="F4" s="9">
+        <f>PRODUCT(E$2:$E3)</f>
+        <v>0.99623084719999999</v>
+      </c>
+      <c r="G4" s="2">
         <v>99615</v>
       </c>
-      <c r="E4" s="3">
+      <c r="H4" s="3">
         <v>79.367400000000004</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -685,20 +746,32 @@
       <c r="C5" s="3">
         <v>1.2999999999999999E-4</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>4.8675344504555822</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99987000000000004</v>
+      </c>
+      <c r="F5" s="9">
+        <f>PRODUCT(E$2:$E4)</f>
+        <v>0.99608141257292004</v>
+      </c>
+      <c r="G5" s="2">
         <v>99602</v>
       </c>
-      <c r="E5" s="3">
+      <c r="H5" s="3">
         <v>78.379310000000004</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -708,20 +781,32 @@
       <c r="C6" s="3">
         <v>1.1E-4</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99988999999999995</v>
+      </c>
+      <c r="F6" s="9">
+        <f>PRODUCT(E$2:$E5)</f>
+        <v>0.99595192198928562</v>
+      </c>
+      <c r="G6" s="2">
         <v>99590</v>
       </c>
-      <c r="E6" s="3">
+      <c r="H6" s="3">
         <v>77.389480000000006</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -731,20 +816,35 @@
       <c r="C7" s="3">
         <v>1E-4</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>4.6051701859880918</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="F7" s="9">
+        <f>PRODUCT(E$2:$E6)</f>
+        <v>0.99584236727786679</v>
+      </c>
+      <c r="G7" s="2">
         <v>99579</v>
       </c>
-      <c r="E7" s="3">
+      <c r="H7" s="3">
         <v>76.398110000000003</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -754,20 +854,35 @@
       <c r="C8" s="3">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
+        <f t="shared" si="0"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99990999999999997</v>
+      </c>
+      <c r="F8" s="9">
+        <f>PRODUCT(E$2:$E7)</f>
+        <v>0.99574278304113906</v>
+      </c>
+      <c r="G8" s="2">
         <v>99570</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>75.405619999999999</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -777,20 +892,32 @@
       <c r="C9" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F9" s="9">
+        <f>PRODUCT(E$2:$E8)</f>
+        <v>0.99565316619066535</v>
+      </c>
+      <c r="G9" s="2">
         <v>99561</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>74.412239999999997</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -800,20 +927,32 @@
       <c r="C10" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F10" s="9">
+        <f>PRODUCT(E$2:$E9)</f>
+        <v>0.99557351393737015</v>
+      </c>
+      <c r="G10" s="2">
         <v>99553</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>73.41825</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -823,20 +962,32 @@
       <c r="C11" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F11" s="9">
+        <f>PRODUCT(E$2:$E10)</f>
+        <v>0.99549386805625517</v>
+      </c>
+      <c r="G11" s="2">
         <v>99546</v>
       </c>
-      <c r="E11" s="3">
+      <c r="H11" s="3">
         <v>72.423940000000002</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -846,20 +997,32 @@
       <c r="C12" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F12" s="9">
+        <f>PRODUCT(E$2:$E11)</f>
+        <v>0.99541422854681072</v>
+      </c>
+      <c r="G12" s="2">
         <v>99538</v>
       </c>
-      <c r="E12" s="3">
+      <c r="H12" s="3">
         <v>71.42953</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -869,20 +1032,32 @@
       <c r="C13" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
+        <f t="shared" si="0"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F13" s="9">
+        <f>PRODUCT(E$2:$E12)</f>
+        <v>0.99533459540852698</v>
+      </c>
+      <c r="G13" s="2">
         <v>99530</v>
       </c>
-      <c r="E13" s="3">
+      <c r="H13" s="3">
         <v>70.435130000000001</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -892,20 +1067,32 @@
       <c r="C14" s="3">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
+        <f t="shared" si="0"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99990999999999997</v>
+      </c>
+      <c r="F14" s="9">
+        <f>PRODUCT(E$2:$E13)</f>
+        <v>0.99525496864089436</v>
+      </c>
+      <c r="G14" s="2">
         <v>99521</v>
       </c>
-      <c r="E14" s="3">
+      <c r="H14" s="3">
         <v>69.440969999999993</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -915,20 +1102,32 @@
       <c r="C15" s="3">
         <v>1.1E-4</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
+        <f t="shared" si="0"/>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99988999999999995</v>
+      </c>
+      <c r="F15" s="9">
+        <f>PRODUCT(E$2:$E14)</f>
+        <v>0.99516539569371665</v>
+      </c>
+      <c r="G15" s="2">
         <v>99511</v>
       </c>
-      <c r="E15" s="3">
+      <c r="H15" s="3">
         <v>68.447310000000002</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -938,20 +1137,32 @@
       <c r="C16" s="3">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
+        <f t="shared" si="0"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99985000000000002</v>
+      </c>
+      <c r="F16" s="9">
+        <f>PRODUCT(E$2:$E15)</f>
+        <v>0.99505592750019023</v>
+      </c>
+      <c r="G16" s="2">
         <v>99498</v>
       </c>
-      <c r="E16" s="3">
+      <c r="H16" s="3">
         <v>67.454989999999995</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -961,20 +1172,32 @@
       <c r="C17" s="3">
         <v>2.1000000000000001E-4</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>5.3471075307174685</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99978999999999996</v>
+      </c>
+      <c r="F17" s="9">
+        <f>PRODUCT(E$2:$E16)</f>
+        <v>0.99490666911106518</v>
+      </c>
+      <c r="G17" s="2">
         <v>99480</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>66.465220000000002</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -984,20 +1207,32 @@
       <c r="C18" s="3">
         <v>2.9E-4</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>5.6698809229805196</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99970999999999999</v>
+      </c>
+      <c r="F18" s="9">
+        <f>PRODUCT(E$2:$E17)</f>
+        <v>0.99469773871055178</v>
+      </c>
+      <c r="G18" s="2">
         <v>99455</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>65.479290000000006</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1007,20 +1242,32 @@
       <c r="C19" s="3">
         <v>3.6999999999999999E-4</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
+        <f t="shared" si="0"/>
+        <v>5.9135030056382698</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99963000000000002</v>
+      </c>
+      <c r="F19" s="9">
+        <f>PRODUCT(E$2:$E18)</f>
+        <v>0.9944092763663257</v>
+      </c>
+      <c r="G19" s="2">
         <v>99422</v>
       </c>
-      <c r="E19" s="3">
+      <c r="H19" s="3">
         <v>64.498090000000005</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1030,20 +1277,32 @@
       <c r="C20" s="3">
         <v>4.4000000000000002E-4</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0867747269123065</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99956</v>
+      </c>
+      <c r="F20" s="9">
+        <f>PRODUCT(E$2:$E19)</f>
+        <v>0.99404134493407015</v>
+      </c>
+      <c r="G20" s="2">
         <v>99382</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>63.521810000000002</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1053,20 +1312,32 @@
       <c r="C21" s="3">
         <v>4.8999999999999998E-4</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>6.1944053911046719</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99951000000000001</v>
+      </c>
+      <c r="F21" s="9">
+        <f>PRODUCT(E$2:$E20)</f>
+        <v>0.99360396674229912</v>
+      </c>
+      <c r="G21" s="2">
         <v>99336</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>62.549390000000002</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I21" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1076,20 +1347,32 @@
       <c r="C22" s="3">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>6.2728770065461674</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99946999999999997</v>
+      </c>
+      <c r="F22" s="9">
+        <f>PRODUCT(E$2:$E21)</f>
+        <v>0.99311710079859539</v>
+      </c>
+      <c r="G22" s="2">
         <v>99285</v>
       </c>
-      <c r="E22" s="3">
+      <c r="H22" s="3">
         <v>61.579900000000002</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1099,20 +1382,32 @@
       <c r="C23" s="3">
         <v>5.5000000000000003E-4</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
+        <f t="shared" si="0"/>
+        <v>6.3099182782265162</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99944999999999995</v>
+      </c>
+      <c r="F23" s="9">
+        <f>PRODUCT(E$2:$E22)</f>
+        <v>0.99259074873517206</v>
+      </c>
+      <c r="G23" s="2">
         <v>99231</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>60.612220000000001</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I23" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1122,20 +1417,32 @@
       <c r="C24" s="3">
         <v>5.5999999999999995E-4</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
+        <f t="shared" si="0"/>
+        <v>6.3279367837291947</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99944</v>
+      </c>
+      <c r="F24" s="9">
+        <f>PRODUCT(E$2:$E23)</f>
+        <v>0.99204482382336767</v>
+      </c>
+      <c r="G24" s="2">
         <v>99176</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>59.645330000000001</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I24" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1145,20 +1452,32 @@
       <c r="C25" s="3">
         <v>5.8E-4</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
+        <f t="shared" si="0"/>
+        <v>6.363028103540465</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99941999999999998</v>
+      </c>
+      <c r="F25" s="9">
+        <f>PRODUCT(E$2:$E24)</f>
+        <v>0.99148927872202663</v>
+      </c>
+      <c r="G25" s="2">
         <v>99119</v>
       </c>
-      <c r="E25" s="3">
+      <c r="H25" s="3">
         <v>58.678649999999998</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1168,20 +1487,32 @@
       <c r="C26" s="3">
         <v>5.9000000000000003E-4</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
+        <f t="shared" si="0"/>
+        <v>6.3801225368997647</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99941000000000002</v>
+      </c>
+      <c r="F26" s="9">
+        <f>PRODUCT(E$2:$E25)</f>
+        <v>0.9909142149403678</v>
+      </c>
+      <c r="G26" s="2">
         <v>99061</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>57.712240000000001</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I26" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1191,20 +1522,32 @@
       <c r="C27" s="3">
         <v>6.0999999999999997E-4</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
+        <f t="shared" si="0"/>
+        <v>6.4134589571673573</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99939</v>
+      </c>
+      <c r="F27" s="9">
+        <f>PRODUCT(E$2:$E26)</f>
+        <v>0.99032957555355305</v>
+      </c>
+      <c r="G27" s="2">
         <v>99002</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>56.746200000000002</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1214,20 +1557,32 @@
       <c r="C28" s="3">
         <v>6.4000000000000005E-4</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
+        <f t="shared" si="0"/>
+        <v>6.4614681763537174</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99936000000000003</v>
+      </c>
+      <c r="F28" s="9">
+        <f>PRODUCT(E$2:$E27)</f>
+        <v>0.9897254745124654</v>
+      </c>
+      <c r="G28" s="2">
         <v>98940</v>
       </c>
-      <c r="E28" s="3">
+      <c r="H28" s="3">
         <v>55.780679999999997</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I28" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1237,20 +1592,32 @@
       <c r="C29" s="3">
         <v>6.6E-4</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>6.4922398350204711</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99934000000000001</v>
+      </c>
+      <c r="F29" s="9">
+        <f>PRODUCT(E$2:$E28)</f>
+        <v>0.98909205020877744</v>
+      </c>
+      <c r="G29" s="2">
         <v>98876</v>
       </c>
-      <c r="E29" s="3">
+      <c r="H29" s="3">
         <v>54.815809999999999</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1260,20 +1627,32 @@
       <c r="C30" s="3">
         <v>6.8999999999999997E-4</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
+        <f t="shared" si="0"/>
+        <v>6.5366915975913047</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99931000000000003</v>
+      </c>
+      <c r="F30" s="9">
+        <f>PRODUCT(E$2:$E29)</f>
+        <v>0.98843924945563966</v>
+      </c>
+      <c r="G30" s="2">
         <v>98809</v>
       </c>
-      <c r="E30" s="3">
+      <c r="H30" s="3">
         <v>53.851779999999998</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1283,20 +1662,32 @@
       <c r="C31" s="3">
         <v>7.1000000000000002E-4</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
+        <f t="shared" si="0"/>
+        <v>6.5652649700353614</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99929000000000001</v>
+      </c>
+      <c r="F31" s="9">
+        <f>PRODUCT(E$2:$E30)</f>
+        <v>0.98775722637351526</v>
+      </c>
+      <c r="G31" s="2">
         <v>98740</v>
       </c>
-      <c r="E31" s="3">
+      <c r="H31" s="3">
         <v>52.888539999999999</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I31" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1306,20 +1697,32 @@
       <c r="C32" s="3">
         <v>7.2999999999999996E-4</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
+        <f t="shared" si="0"/>
+        <v>6.5930445341424369</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99926999999999999</v>
+      </c>
+      <c r="F32" s="9">
+        <f>PRODUCT(E$2:$E31)</f>
+        <v>0.98705591874279008</v>
+      </c>
+      <c r="G32" s="2">
         <v>98669</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>51.92577</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1329,20 +1732,32 @@
       <c r="C33" s="3">
         <v>7.6000000000000004E-4</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
+        <f t="shared" si="0"/>
+        <v>6.633318433280377</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99924000000000002</v>
+      </c>
+      <c r="F33" s="9">
+        <f>PRODUCT(E$2:$E32)</f>
+        <v>0.98633536792210785</v>
+      </c>
+      <c r="G33" s="2">
         <v>98595</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>50.963419999999999</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I33" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1352,20 +1767,32 @@
       <c r="C34" s="3">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
+        <f t="shared" si="0"/>
+        <v>6.6720329454610674</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99921000000000004</v>
+      </c>
+      <c r="F34" s="9">
+        <f>PRODUCT(E$2:$E33)</f>
+        <v>0.98558575304248708</v>
+      </c>
+      <c r="G34" s="2">
         <v>98519</v>
       </c>
-      <c r="E34" s="3">
+      <c r="H34" s="3">
         <v>50.001660000000001</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -1375,20 +1802,32 @@
       <c r="C35" s="3">
         <v>8.3000000000000001E-4</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
+        <f t="shared" si="0"/>
+        <v>6.7214257007906433</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99917</v>
+      </c>
+      <c r="F35" s="9">
+        <f>PRODUCT(E$2:$E34)</f>
+        <v>0.98480714029758354</v>
+      </c>
+      <c r="G35" s="2">
         <v>98440</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>49.040770000000002</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I35" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -1398,20 +1837,32 @@
       <c r="C36" s="3">
         <v>8.7000000000000001E-4</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
+        <f t="shared" si="0"/>
+        <v>6.7684932116486296</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99912999999999996</v>
+      </c>
+      <c r="F36" s="9">
+        <f>PRODUCT(E$2:$E35)</f>
+        <v>0.98398975037113656</v>
+      </c>
+      <c r="G36" s="2">
         <v>98356</v>
       </c>
-      <c r="E36" s="3">
+      <c r="H36" s="3">
         <v>48.080919999999999</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I36" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1421,20 +1872,32 @@
       <c r="C37" s="3">
         <v>9.1E-4</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
+        <f t="shared" si="0"/>
+        <v>6.8134445995108956</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99909000000000003</v>
+      </c>
+      <c r="F37" s="9">
+        <f>PRODUCT(E$2:$E36)</f>
+        <v>0.98313367928831363</v>
+      </c>
+      <c r="G37" s="2">
         <v>98269</v>
       </c>
-      <c r="E37" s="3">
+      <c r="H37" s="3">
         <v>47.122140000000002</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I37" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -1444,20 +1907,32 @@
       <c r="C38" s="3">
         <v>9.6000000000000002E-4</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
+        <f t="shared" si="0"/>
+        <v>6.866933284461882</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99904000000000004</v>
+      </c>
+      <c r="F38" s="9">
+        <f>PRODUCT(E$2:$E37)</f>
+        <v>0.98223902764016136</v>
+      </c>
+      <c r="G38" s="2">
         <v>98178</v>
       </c>
-      <c r="E38" s="3">
+      <c r="H38" s="3">
         <v>46.16451</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -1467,20 +1942,32 @@
       <c r="C39" s="3">
         <v>1.0200000000000001E-3</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
+        <f t="shared" si="0"/>
+        <v>6.9275579062783166</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99897999999999998</v>
+      </c>
+      <c r="F39" s="9">
+        <f>PRODUCT(E$2:$E38)</f>
+        <v>0.98129607817362685</v>
+      </c>
+      <c r="G39" s="2">
         <v>98081</v>
       </c>
-      <c r="E39" s="3">
+      <c r="H39" s="3">
         <v>45.208199999999998</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -1490,20 +1977,32 @@
       <c r="C40" s="3">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
+        <f t="shared" si="0"/>
+        <v>7.0030654587864616</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99890000000000001</v>
+      </c>
+      <c r="F40" s="9">
+        <f>PRODUCT(E$2:$E39)</f>
+        <v>0.98029515617388974</v>
+      </c>
+      <c r="G40" s="2">
         <v>97977</v>
       </c>
-      <c r="E40" s="3">
+      <c r="H40" s="3">
         <v>44.25376</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -1513,20 +2012,32 @@
       <c r="C41" s="3">
         <v>1.1900000000000001E-3</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
+        <f t="shared" si="0"/>
+        <v>7.0817085861055746</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99880999999999998</v>
+      </c>
+      <c r="F41" s="9">
+        <f>PRODUCT(E$2:$E40)</f>
+        <v>0.97921683150209848</v>
+      </c>
+      <c r="G41" s="2">
         <v>97865</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>43.301859999999998</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -1536,20 +2047,32 @@
       <c r="C42" s="3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
+        <f t="shared" si="0"/>
+        <v>7.1701195434496281</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99870000000000003</v>
+      </c>
+      <c r="F42" s="9">
+        <f>PRODUCT(E$2:$E41)</f>
+        <v>0.97805156347261091</v>
+      </c>
+      <c r="G42" s="2">
         <v>97743</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>42.353050000000003</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -1559,20 +2082,32 @@
       <c r="C43" s="3">
         <v>1.42E-3</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>7.2584121505953068</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99858000000000002</v>
+      </c>
+      <c r="F43" s="9">
+        <f>PRODUCT(E$2:$E42)</f>
+        <v>0.97678009644009656</v>
+      </c>
+      <c r="G43" s="2">
         <v>97609</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>41.407730000000001</v>
       </c>
-      <c r="F43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -1582,20 +2117,32 @@
       <c r="C44" s="3">
         <v>1.5499999999999999E-3</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
+        <f t="shared" si="0"/>
+        <v>7.3460102099132927</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99844999999999995</v>
+      </c>
+      <c r="F44" s="9">
+        <f>PRODUCT(E$2:$E43)</f>
+        <v>0.97539306870315168</v>
+      </c>
+      <c r="G44" s="2">
         <v>97465</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>40.465989999999998</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -1605,20 +2152,32 @@
       <c r="C45" s="3">
         <v>1.6800000000000001E-3</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
+        <f t="shared" si="0"/>
+        <v>7.4265490723973047</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99831999999999999</v>
+      </c>
+      <c r="F45" s="9">
+        <f>PRODUCT(E$2:$E44)</f>
+        <v>0.97388120944666179</v>
+      </c>
+      <c r="G45" s="2">
         <v>97307</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>39.527909999999999</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I45" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -1628,20 +2187,32 @@
       <c r="C46" s="3">
         <v>1.82E-3</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
+        <f t="shared" si="0"/>
+        <v>7.506591780070841</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99817999999999996</v>
+      </c>
+      <c r="F46" s="9">
+        <f>PRODUCT(E$2:$E45)</f>
+        <v>0.97224508901479134</v>
+      </c>
+      <c r="G46" s="2">
         <v>97137</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>38.593649999999997</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -1651,20 +2222,32 @@
       <c r="C47" s="3">
         <v>1.9599999999999999E-3</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
+        <f t="shared" si="0"/>
+        <v>7.5806997522245627</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99804000000000004</v>
+      </c>
+      <c r="F47" s="9">
+        <f>PRODUCT(E$2:$E46)</f>
+        <v>0.97047560295278434</v>
+      </c>
+      <c r="G47" s="2">
         <v>96953</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>37.663159999999998</v>
       </c>
-      <c r="F47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -1674,20 +2257,32 @@
       <c r="C48" s="3">
         <v>2.0899999999999998E-3</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
+        <f t="shared" si="0"/>
+        <v>7.6449193449588568</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99790999999999996</v>
+      </c>
+      <c r="F48" s="9">
+        <f>PRODUCT(E$2:$E47)</f>
+        <v>0.96857347077099687</v>
+      </c>
+      <c r="G48" s="2">
         <v>96757</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>36.736020000000003</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -1697,20 +2292,32 @@
       <c r="C49" s="3">
         <v>2.2399999999999998E-3</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
+        <f t="shared" si="0"/>
+        <v>7.7142311448490855</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99775999999999998</v>
+      </c>
+      <c r="F49" s="9">
+        <f>PRODUCT(E$2:$E48)</f>
+        <v>0.96654915221708548</v>
+      </c>
+      <c r="G49" s="2">
         <v>96548</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>35.811770000000003</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -1720,20 +2327,32 @@
       <c r="C50" s="3">
         <v>2.4099999999999998E-3</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
+        <f t="shared" si="0"/>
+        <v>7.7873820264847007</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99758999999999998</v>
+      </c>
+      <c r="F50" s="9">
+        <f>PRODUCT(E$2:$E49)</f>
+        <v>0.96438408211611915</v>
+      </c>
+      <c r="G50" s="2">
         <v>96324</v>
       </c>
-      <c r="E50" s="3">
+      <c r="H50" s="3">
         <v>34.890949999999997</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -1743,20 +2362,32 @@
       <c r="C51" s="3">
         <v>2.6099999999999999E-3</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
+        <f t="shared" si="0"/>
+        <v>7.8671055003167387</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99739</v>
+      </c>
+      <c r="F51" s="9">
+        <f>PRODUCT(E$2:$E50)</f>
+        <v>0.96205991647821931</v>
+      </c>
+      <c r="G51" s="2">
         <v>96083</v>
       </c>
-      <c r="E51" s="3">
+      <c r="H51" s="3">
         <v>33.97401</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -1766,20 +2397,32 @@
       <c r="C52" s="3">
         <v>2.8400000000000001E-3</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
+        <f t="shared" si="0"/>
+        <v>7.9515593311552522</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99716000000000005</v>
+      </c>
+      <c r="F52" s="9">
+        <f>PRODUCT(E$2:$E51)</f>
+        <v>0.95954894009621117</v>
+      </c>
+      <c r="G52" s="2">
         <v>95821</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>33.061669999999999</v>
       </c>
-      <c r="F52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -1789,20 +2432,32 @@
       <c r="C53" s="3">
         <v>3.0899999999999999E-3</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="3">
+        <f t="shared" si="0"/>
+        <v>8.0359263698917918</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99690999999999996</v>
+      </c>
+      <c r="F53" s="9">
+        <f>PRODUCT(E$2:$E52)</f>
+        <v>0.95682382110633801</v>
+      </c>
+      <c r="G53" s="2">
         <v>95537</v>
       </c>
-      <c r="E53" s="3">
+      <c r="H53" s="3">
         <v>32.154400000000003</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -1812,20 +2467,32 @@
       <c r="C54" s="3">
         <v>3.3500000000000001E-3</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
+        <f t="shared" si="0"/>
+        <v>8.1167156248191112</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99665000000000004</v>
+      </c>
+      <c r="F54" s="9">
+        <f>PRODUCT(E$2:$E53)</f>
+        <v>0.95386723549911945</v>
+      </c>
+      <c r="G54" s="2">
         <v>95230</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>31.252379999999999</v>
       </c>
-      <c r="F54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1835,20 +2502,32 @@
       <c r="C55" s="3">
         <v>3.63E-3</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
+        <f t="shared" si="0"/>
+        <v>8.1969879272588972</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99636999999999998</v>
+      </c>
+      <c r="F55" s="9">
+        <f>PRODUCT(E$2:$E54)</f>
+        <v>0.95067178026019739</v>
+      </c>
+      <c r="G55" s="2">
         <v>94897</v>
       </c>
-      <c r="E55" s="3">
+      <c r="H55" s="3">
         <v>30.355730000000001</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -1858,20 +2537,32 @@
       <c r="C56" s="3">
         <v>3.9399999999999999E-3</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
+        <f t="shared" si="0"/>
+        <v>8.2789360022919798</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99605999999999995</v>
+      </c>
+      <c r="F56" s="9">
+        <f>PRODUCT(E$2:$E55)</f>
+        <v>0.94722084169785281</v>
+      </c>
+      <c r="G56" s="2">
         <v>94538</v>
       </c>
-      <c r="E56" s="3">
+      <c r="H56" s="3">
         <v>29.464479999999998</v>
       </c>
-      <c r="F56" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -1881,20 +2572,32 @@
       <c r="C57" s="3">
         <v>4.2700000000000004E-3</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
+        <f t="shared" si="0"/>
+        <v>8.3593691062226707</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99573</v>
+      </c>
+      <c r="F57" s="9">
+        <f>PRODUCT(E$2:$E56)</f>
+        <v>0.94348879158156318</v>
+      </c>
+      <c r="G57" s="2">
         <v>94150</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>28.5791</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I57" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -1904,20 +2607,32 @@
       <c r="C58" s="3">
         <v>4.6299999999999996E-3</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
+        <f t="shared" si="0"/>
+        <v>8.4403121470802791</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99536999999999998</v>
+      </c>
+      <c r="F58" s="9">
+        <f>PRODUCT(E$2:$E57)</f>
+        <v>0.93946009444150991</v>
+      </c>
+      <c r="G58" s="2">
         <v>93731</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>27.69961</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I58" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -1927,20 +2642,32 @@
       <c r="C59" s="3">
         <v>5.0400000000000002E-3</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
+        <f t="shared" si="0"/>
+        <v>8.5251613610654147</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99495999999999996</v>
+      </c>
+      <c r="F59" s="9">
+        <f>PRODUCT(E$2:$E58)</f>
+        <v>0.93511039420424569</v>
+      </c>
+      <c r="G59" s="2">
         <v>93278</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>26.8262</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I59" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -1950,20 +2677,32 @@
       <c r="C60" s="3">
         <v>5.4900000000000001E-3</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
+        <f t="shared" si="0"/>
+        <v>8.6106835345035755</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99451000000000001</v>
+      </c>
+      <c r="F60" s="9">
+        <f>PRODUCT(E$2:$E59)</f>
+        <v>0.93039743781745621</v>
+      </c>
+      <c r="G60" s="2">
         <v>92788</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>25.959520000000001</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I60" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -1973,20 +2712,32 @@
       <c r="C61" s="3">
         <v>5.9699999999999996E-3</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
+        <f t="shared" si="0"/>
+        <v>8.6945022063866482</v>
+      </c>
+      <c r="E61" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99402999999999997</v>
+      </c>
+      <c r="F61" s="9">
+        <f>PRODUCT(E$2:$E60)</f>
+        <v>0.92528955588383843</v>
+      </c>
+      <c r="G61" s="2">
         <v>92256</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>25.099900000000002</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I61" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -1996,20 +2747,32 @@
       <c r="C62" s="3">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
+        <f t="shared" si="0"/>
+        <v>8.7795574558837277</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99350000000000005</v>
+      </c>
+      <c r="F62" s="9">
+        <f>PRODUCT(E$2:$E61)</f>
+        <v>0.91976557723521191</v>
+      </c>
+      <c r="G62" s="2">
         <v>91681</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>24.247669999999999</v>
       </c>
-      <c r="F62" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I62" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -2019,20 +2782,32 @@
       <c r="C63" s="3">
         <v>7.0699999999999999E-3</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="3">
+        <f t="shared" si="0"/>
+        <v>8.863615758890619</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99292999999999998</v>
+      </c>
+      <c r="F63" s="9">
+        <f>PRODUCT(E$2:$E62)</f>
+        <v>0.91378710098318305</v>
+      </c>
+      <c r="G63" s="2">
         <v>91060</v>
       </c>
-      <c r="E63" s="3">
+      <c r="H63" s="3">
         <v>23.40305</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -2042,20 +2817,32 @@
       <c r="C64" s="3">
         <v>7.6800000000000002E-3</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
+        <f t="shared" si="0"/>
+        <v>8.9463748261417173</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99231999999999998</v>
+      </c>
+      <c r="F64" s="9">
+        <f>PRODUCT(E$2:$E63)</f>
+        <v>0.90732662617923188</v>
+      </c>
+      <c r="G64" s="2">
         <v>90389</v>
       </c>
-      <c r="E64" s="3">
+      <c r="H64" s="3">
         <v>22.56598</v>
       </c>
-      <c r="F64" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I64" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -2065,20 +2852,32 @@
       <c r="C65" s="3">
         <v>8.3400000000000002E-3</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
+        <f t="shared" si="0"/>
+        <v>9.0288184953527928</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99165999999999999</v>
+      </c>
+      <c r="F65" s="9">
+        <f>PRODUCT(E$2:$E64)</f>
+        <v>0.90035835769017536</v>
+      </c>
+      <c r="G65" s="2">
         <v>89666</v>
       </c>
-      <c r="E65" s="3">
+      <c r="H65" s="3">
         <v>21.736630000000002</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I65" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -2088,20 +2887,32 @@
       <c r="C66" s="3">
         <v>9.0900000000000009E-3</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
+        <f t="shared" si="0"/>
+        <v>9.1149301871715238</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99090999999999996</v>
+      </c>
+      <c r="F66" s="9">
+        <f>PRODUCT(E$2:$E65)</f>
+        <v>0.89284936898703926</v>
+      </c>
+      <c r="G66" s="2">
         <v>88885</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>20.915189999999999</v>
       </c>
-      <c r="F66" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I66" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -2111,20 +2922,32 @@
       <c r="C67" s="3">
         <v>9.8899999999999995E-3</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="3">
+        <f t="shared" ref="D67:D130" si="2">LN(10^6*C67)</f>
+        <v>9.1992794246167584</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" si="1"/>
+        <v>0.99011000000000005</v>
+      </c>
+      <c r="F67" s="9">
+        <f>PRODUCT(E$2:$E66)</f>
+        <v>0.88473336822294701</v>
+      </c>
+      <c r="G67" s="2">
         <v>88042</v>
       </c>
-      <c r="E67" s="3">
+      <c r="H67" s="3">
         <v>20.1023</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I67" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -2134,20 +2957,32 @@
       <c r="C68" s="3">
         <v>1.076E-2</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="3">
+        <f t="shared" si="2"/>
+        <v>9.2835908337157758</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" ref="E68:E131" si="3">1-C68</f>
+        <v>0.98924000000000001</v>
+      </c>
+      <c r="F68" s="9">
+        <f>PRODUCT(E$2:$E67)</f>
+        <v>0.87598335521122206</v>
+      </c>
+      <c r="G68" s="2">
         <v>87134</v>
       </c>
-      <c r="E68" s="3">
+      <c r="H68" s="3">
         <v>19.29806</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I68" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -2157,20 +2992,32 @@
       <c r="C69" s="3">
         <v>1.172E-2</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
+        <f t="shared" si="2"/>
+        <v>9.3690520631310044</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98828000000000005</v>
+      </c>
+      <c r="F69" s="9">
+        <f>PRODUCT(E$2:$E68)</f>
+        <v>0.86655777430914926</v>
+      </c>
+      <c r="G69" s="2">
         <v>86155</v>
       </c>
-      <c r="E69" s="3">
+      <c r="H69" s="3">
         <v>18.502410000000001</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I69" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -2180,20 +3027,32 @@
       <c r="C70" s="3">
         <v>1.278E-2</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="3">
+        <f t="shared" si="2"/>
+        <v>9.455636727931525</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98721999999999999</v>
+      </c>
+      <c r="F70" s="9">
+        <f>PRODUCT(E$2:$E69)</f>
+        <v>0.85640171719424607</v>
+      </c>
+      <c r="G70" s="2">
         <v>85101</v>
       </c>
-      <c r="E70" s="3">
+      <c r="H70" s="3">
         <v>17.71575</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I70" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -2203,20 +3062,32 @@
       <c r="C71" s="3">
         <v>1.391E-2</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3">
+        <f t="shared" si="2"/>
+        <v>9.540363284917488</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98609000000000002</v>
+      </c>
+      <c r="F71" s="9">
+        <f>PRODUCT(E$2:$E70)</f>
+        <v>0.84545690324850364</v>
+      </c>
+      <c r="G71" s="2">
         <v>83967</v>
       </c>
-      <c r="E71" s="3">
+      <c r="H71" s="3">
         <v>16.93845</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I71" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -2226,20 +3097,32 @@
       <c r="C72" s="3">
         <v>1.5180000000000001E-2</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="3">
+        <f t="shared" si="2"/>
+        <v>9.6277340509496216</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98482000000000003</v>
+      </c>
+      <c r="F72" s="9">
+        <f>PRODUCT(E$2:$E71)</f>
+        <v>0.83369659772431692</v>
+      </c>
+      <c r="G72" s="2">
         <v>82746</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>16.170249999999999</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I72" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -2249,20 +3132,32 @@
       <c r="C73" s="3">
         <v>1.66E-2</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="3">
+        <f t="shared" si="2"/>
+        <v>9.7171579743446355</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="F73" s="9">
+        <f>PRODUCT(E$2:$E72)</f>
+        <v>0.82104108337086179</v>
+      </c>
+      <c r="G73" s="2">
         <v>81433</v>
       </c>
-      <c r="E73" s="3">
+      <c r="H73" s="3">
         <v>15.411759999999999</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I73" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -2272,20 +3167,32 @@
       <c r="C74" s="3">
         <v>1.823E-2</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="3">
+        <f t="shared" si="2"/>
+        <v>9.810823867672708</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="3"/>
+        <v>0.98177000000000003</v>
+      </c>
+      <c r="F74" s="9">
+        <f>PRODUCT(E$2:$E73)</f>
+        <v>0.80741180138690549</v>
+      </c>
+      <c r="G74" s="2">
         <v>80016</v>
       </c>
-      <c r="E74" s="3">
+      <c r="H74" s="3">
         <v>14.66338</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I74" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -2295,20 +3202,32 @@
       <c r="C75" s="3">
         <v>2.0109999999999999E-2</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="3">
+        <f t="shared" si="2"/>
+        <v>9.9089724827666981</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="3"/>
+        <v>0.97989000000000004</v>
+      </c>
+      <c r="F75" s="9">
+        <f>PRODUCT(E$2:$E74)</f>
+        <v>0.79269268424762218</v>
+      </c>
+      <c r="G75" s="2">
         <v>78484</v>
       </c>
-      <c r="E75" s="3">
+      <c r="H75" s="3">
         <v>13.92628</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I75" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -2318,20 +3237,32 @@
       <c r="C76" s="3">
         <v>2.2259999999999999E-2</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="3">
+        <f t="shared" si="2"/>
+        <v>10.010546624829535</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" si="3"/>
+        <v>0.97774000000000005</v>
+      </c>
+      <c r="F76" s="9">
+        <f>PRODUCT(E$2:$E75)</f>
+        <v>0.77675163436740258</v>
+      </c>
+      <c r="G76" s="2">
         <v>76824</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>13.20172</v>
       </c>
-      <c r="F76" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I76" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -2341,20 +3272,32 @@
       <c r="C77" s="3">
         <v>2.4709999999999999E-2</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="3">
+        <f t="shared" si="2"/>
+        <v>10.114963298982655</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" si="3"/>
+        <v>0.97528999999999999</v>
+      </c>
+      <c r="F77" s="9">
+        <f>PRODUCT(E$2:$E76)</f>
+        <v>0.75946114298638423</v>
+      </c>
+      <c r="G77" s="2">
         <v>75022</v>
       </c>
-      <c r="E77" s="3">
+      <c r="H77" s="3">
         <v>12.49075</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I77" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -2364,20 +3307,32 @@
       <c r="C78" s="3">
         <v>2.7529999999999999E-2</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="3">
+        <f t="shared" si="2"/>
+        <v>10.223031598136654</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" si="3"/>
+        <v>0.97246999999999995</v>
+      </c>
+      <c r="F78" s="9">
+        <f>PRODUCT(E$2:$E77)</f>
+        <v>0.74069485814319069</v>
+      </c>
+      <c r="G78" s="2">
         <v>73066</v>
       </c>
-      <c r="E78" s="3">
+      <c r="H78" s="3">
         <v>11.794359999999999</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I78" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -2387,20 +3342,32 @@
       <c r="C79" s="3">
         <v>3.083E-2</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="3">
+        <f t="shared" si="2"/>
+        <v>10.336243520880195</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" si="3"/>
+        <v>0.96916999999999998</v>
+      </c>
+      <c r="F79" s="9">
+        <f>PRODUCT(E$2:$E78)</f>
+        <v>0.72030352869850867</v>
+      </c>
+      <c r="G79" s="2">
         <v>70938</v>
       </c>
-      <c r="E79" s="3">
+      <c r="H79" s="3">
         <v>11.113899999999999</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I79" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -2410,20 +3377,32 @@
       <c r="C80" s="3">
         <v>3.465E-2</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="3">
+        <f t="shared" si="2"/>
+        <v>10.453053004618049</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" si="3"/>
+        <v>0.96535000000000004</v>
+      </c>
+      <c r="F80" s="9">
+        <f>PRODUCT(E$2:$E79)</f>
+        <v>0.69809657090873367</v>
+      </c>
+      <c r="G80" s="2">
         <v>68619</v>
       </c>
-      <c r="E80" s="3">
+      <c r="H80" s="3">
         <v>10.45125</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I80" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -2433,20 +3412,32 @@
       <c r="C81" s="3">
         <v>3.9059999999999997E-2</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="3">
+        <f t="shared" si="2"/>
+        <v>10.572854204430669</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" si="3"/>
+        <v>0.96094000000000002</v>
+      </c>
+      <c r="F81" s="9">
+        <f>PRODUCT(E$2:$E80)</f>
+        <v>0.67390752472674609</v>
+      </c>
+      <c r="G81" s="2">
         <v>66095</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>9.8082100000000008</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I81" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -2456,20 +3447,32 @@
       <c r="C82" s="3">
         <v>4.4040000000000003E-2</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="3">
+        <f t="shared" si="2"/>
+        <v>10.692853590836616</v>
+      </c>
+      <c r="E82" s="3">
+        <f t="shared" si="3"/>
+        <v>0.95596000000000003</v>
+      </c>
+      <c r="F82" s="9">
+        <f>PRODUCT(E$2:$E81)</f>
+        <v>0.64758469681091935</v>
+      </c>
+      <c r="G82" s="2">
         <v>63354</v>
       </c>
-      <c r="E82" s="3">
+      <c r="H82" s="3">
         <v>9.1862200000000005</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I82" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -2479,20 +3482,32 @@
       <c r="C83" s="3">
         <v>4.9549999999999997E-2</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="3">
+        <f t="shared" si="2"/>
+        <v>10.810737539758135</v>
+      </c>
+      <c r="E83" s="3">
+        <f t="shared" si="3"/>
+        <v>0.95045000000000002</v>
+      </c>
+      <c r="F83" s="9">
+        <f>PRODUCT(E$2:$E82)</f>
+        <v>0.61906506676336648</v>
+      </c>
+      <c r="G83" s="2">
         <v>60394</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>8.5860299999999992</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I83" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -2502,20 +3517,32 @@
       <c r="C84" s="3">
         <v>5.5780000000000003E-2</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="3">
+        <f t="shared" si="2"/>
+        <v>10.92917066118148</v>
+      </c>
+      <c r="E84" s="3">
+        <f t="shared" si="3"/>
+        <v>0.94421999999999995</v>
+      </c>
+      <c r="F84" s="9">
+        <f>PRODUCT(E$2:$E83)</f>
+        <v>0.58839039270524163</v>
+      </c>
+      <c r="G84" s="2">
         <v>57220</v>
       </c>
-      <c r="E84" s="3">
+      <c r="H84" s="3">
         <v>8.0071999999999992</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I84" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -2525,20 +3552,32 @@
       <c r="C85" s="3">
         <v>6.2979999999999994E-2</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="3">
+        <f t="shared" si="2"/>
+        <v>11.050572494655016</v>
+      </c>
+      <c r="E85" s="3">
+        <f t="shared" si="3"/>
+        <v>0.93701999999999996</v>
+      </c>
+      <c r="F85" s="9">
+        <f>PRODUCT(E$2:$E84)</f>
+        <v>0.55556997660014318</v>
+      </c>
+      <c r="G85" s="2">
         <v>53830</v>
       </c>
-      <c r="E85" s="3">
+      <c r="H85" s="3">
         <v>7.4503399999999997</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I85" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -2548,20 +3587,32 @@
       <c r="C86" s="3">
         <v>7.1279999999999996E-2</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="3">
+        <f t="shared" si="2"/>
+        <v>11.17437106214469</v>
+      </c>
+      <c r="E86" s="3">
+        <f t="shared" si="3"/>
+        <v>0.92871999999999999</v>
+      </c>
+      <c r="F86" s="9">
+        <f>PRODUCT(E$2:$E85)</f>
+        <v>0.52058017947386614</v>
+      </c>
+      <c r="G86" s="2">
         <v>50225</v>
       </c>
-      <c r="E86" s="3">
+      <c r="H86" s="3">
         <v>6.9170699999999998</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I86" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -2571,20 +3622,32 @@
       <c r="C87" s="3">
         <v>8.0890000000000004E-2</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="3">
+        <f t="shared" si="2"/>
+        <v>11.300845486011998</v>
+      </c>
+      <c r="E87" s="3">
+        <f t="shared" si="3"/>
+        <v>0.91910999999999998</v>
+      </c>
+      <c r="F87" s="9">
+        <f>PRODUCT(E$2:$E86)</f>
+        <v>0.48347322428096895</v>
+      </c>
+      <c r="G87" s="2">
         <v>46414</v>
       </c>
-      <c r="E87" s="3">
+      <c r="H87" s="3">
         <v>6.40916</v>
       </c>
-      <c r="F87" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I87" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -2594,20 +3657,32 @@
       <c r="C88" s="3">
         <v>9.1859999999999997E-2</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="3">
+        <f t="shared" si="2"/>
+        <v>11.428020957879784</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" si="3"/>
+        <v>0.90813999999999995</v>
+      </c>
+      <c r="F88" s="9">
+        <f>PRODUCT(E$2:$E87)</f>
+        <v>0.44436507516888135</v>
+      </c>
+      <c r="G88" s="2">
         <v>42414</v>
       </c>
-      <c r="E88" s="3">
+      <c r="H88" s="3">
         <v>5.9287599999999996</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I88" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -2617,20 +3692,32 @@
       <c r="C89" s="3">
         <v>0.10414</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="3">
+        <f t="shared" si="2"/>
+        <v>11.55349142671689</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" si="3"/>
+        <v>0.89585999999999999</v>
+      </c>
+      <c r="F89" s="9">
+        <f>PRODUCT(E$2:$E88)</f>
+        <v>0.40354569936386786</v>
+      </c>
+      <c r="G89" s="2">
         <v>38268</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>5.4774599999999998</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I89" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -2640,20 +3727,32 @@
       <c r="C90" s="3">
         <v>0.11786000000000001</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="3">
+        <f t="shared" si="2"/>
+        <v>11.677252758391905</v>
+      </c>
+      <c r="E90" s="3">
+        <f t="shared" si="3"/>
+        <v>0.88214000000000004</v>
+      </c>
+      <c r="F90" s="9">
+        <f>PRODUCT(E$2:$E89)</f>
+        <v>0.36152045023211465</v>
+      </c>
+      <c r="G90" s="2">
         <v>34031</v>
       </c>
-      <c r="E90" s="3">
+      <c r="H90" s="3">
         <v>5.0556599999999996</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I90" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -2663,20 +3762,32 @@
       <c r="C91" s="3">
         <v>0.1331</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="3">
+        <f t="shared" si="2"/>
+        <v>11.798856004383204</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" si="3"/>
+        <v>0.8669</v>
+      </c>
+      <c r="F91" s="9">
+        <f>PRODUCT(E$2:$E90)</f>
+        <v>0.31891164996775762</v>
+      </c>
+      <c r="G91" s="2">
         <v>29771</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>4.66404</v>
       </c>
-      <c r="F91" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I91" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -2686,20 +3797,32 @@
       <c r="C92" s="3">
         <v>0.14993999999999999</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="3">
+        <f t="shared" si="2"/>
+        <v>11.917990493057053</v>
+      </c>
+      <c r="E92" s="3">
+        <f t="shared" si="3"/>
+        <v>0.85006000000000004</v>
+      </c>
+      <c r="F92" s="9">
+        <f>PRODUCT(E$2:$E91)</f>
+        <v>0.27646450935704908</v>
+      </c>
+      <c r="G92" s="2">
         <v>25568</v>
       </c>
-      <c r="E92" s="3">
+      <c r="H92" s="3">
         <v>4.3032899999999996</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I92" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -2709,20 +3832,32 @@
       <c r="C93" s="3">
         <v>0.16836999999999999</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="3">
+        <f t="shared" si="2"/>
+        <v>12.033919217651846</v>
+      </c>
+      <c r="E93" s="3">
+        <f t="shared" si="3"/>
+        <v>0.83162999999999998</v>
+      </c>
+      <c r="F93" s="9">
+        <f>PRODUCT(E$2:$E92)</f>
+        <v>0.23501142082405316</v>
+      </c>
+      <c r="G93" s="2">
         <v>21508</v>
       </c>
-      <c r="E93" s="3">
+      <c r="H93" s="3">
         <v>3.9743400000000002</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I93" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -2732,20 +3867,32 @@
       <c r="C94" s="3">
         <v>0.18790999999999999</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="3">
+        <f t="shared" si="2"/>
+        <v>12.143718403783199</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="3"/>
+        <v>0.81208999999999998</v>
+      </c>
+      <c r="F94" s="9">
+        <f>PRODUCT(E$2:$E93)</f>
+        <v>0.19544254789990731</v>
+      </c>
+      <c r="G94" s="2">
         <v>17683</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>3.6785000000000001</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I94" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -2755,20 +3902,32 @@
       <c r="C95" s="3">
         <v>0.20821999999999999</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="3">
+        <f t="shared" si="2"/>
+        <v>12.246350492028744</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="3"/>
+        <v>0.79178000000000004</v>
+      </c>
+      <c r="F95" s="9">
+        <f>PRODUCT(E$2:$E94)</f>
+        <v>0.15871693872403572</v>
+      </c>
+      <c r="G95" s="2">
         <v>14187</v>
       </c>
-      <c r="E95" s="3">
+      <c r="H95" s="3">
         <v>3.41554</v>
       </c>
-      <c r="F95" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I95" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -2778,20 +3937,32 @@
       <c r="C96" s="3">
         <v>0.22978000000000001</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="3">
+        <f t="shared" si="2"/>
+        <v>12.344877608407355</v>
+      </c>
+      <c r="E96" s="3">
+        <f t="shared" si="3"/>
+        <v>0.77022000000000002</v>
+      </c>
+      <c r="F96" s="9">
+        <f>PRODUCT(E$2:$E95)</f>
+        <v>0.12566889774291701</v>
+      </c>
+      <c r="G96" s="2">
         <v>11077</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
         <v>3.1848299999999998</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I96" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -2801,20 +3972,32 @@
       <c r="C97" s="3">
         <v>0.24532000000000001</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="3">
+        <f t="shared" si="2"/>
+        <v>12.410318759739919</v>
+      </c>
+      <c r="E97" s="3">
+        <f t="shared" si="3"/>
+        <v>0.75468000000000002</v>
+      </c>
+      <c r="F97" s="9">
+        <f>PRODUCT(E$2:$E96)</f>
+        <v>9.6792698419549544E-2</v>
+      </c>
+      <c r="G97" s="2">
         <v>8446</v>
       </c>
-      <c r="E97" s="3">
+      <c r="H97" s="3">
         <v>2.9905400000000002</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I97" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -2824,20 +4007,32 @@
       <c r="C98" s="3">
         <v>0.26695999999999998</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="3">
+        <f t="shared" si="2"/>
+        <v>12.494854113425255</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="3"/>
+        <v>0.73304000000000002</v>
+      </c>
+      <c r="F98" s="9">
+        <f>PRODUCT(E$2:$E97)</f>
+        <v>7.3047513643265657E-2</v>
+      </c>
+      <c r="G98" s="2">
         <v>6284</v>
       </c>
-      <c r="E98" s="3">
+      <c r="H98" s="3">
         <v>2.8063600000000002</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I98" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -2847,20 +4042,32 @@
       <c r="C99" s="3">
         <v>0.28100000000000003</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="3">
+        <f t="shared" si="2"/>
+        <v>12.546109948315882</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="3"/>
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="F99" s="9">
+        <f>PRODUCT(E$2:$E98)</f>
+        <v>5.3546749401059461E-2</v>
+      </c>
+      <c r="G99" s="2">
         <v>4559</v>
       </c>
-      <c r="E99" s="3">
+      <c r="H99" s="3">
         <v>2.65482</v>
       </c>
-      <c r="F99" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I99" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -2870,20 +4077,32 @@
       <c r="C100" s="3">
         <v>0.29874000000000001</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="3">
+        <f t="shared" si="2"/>
+        <v>12.607328908864284</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="3"/>
+        <v>0.70125999999999999</v>
+      </c>
+      <c r="F100" s="9">
+        <f>PRODUCT(E$2:$E99)</f>
+        <v>3.8500112819361748E-2</v>
+      </c>
+      <c r="G100" s="2">
         <v>3240</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>2.5082200000000001</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I100" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -2893,20 +4112,32 @@
       <c r="C101" s="3">
         <v>0.31625999999999999</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="3">
+        <f t="shared" si="2"/>
+        <v>12.664319939077307</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" si="3"/>
+        <v>0.68374000000000001</v>
+      </c>
+      <c r="F101" s="9">
+        <f>PRODUCT(E$2:$E100)</f>
+        <v>2.6998589115705619E-2</v>
+      </c>
+      <c r="G101" s="2">
         <v>2242</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>2.3767999999999998</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I101" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -2916,20 +4147,32 @@
       <c r="C102" s="3">
         <v>0.33077000000000001</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="3">
+        <f t="shared" si="2"/>
+        <v>12.709178548780946</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" si="3"/>
+        <v>0.66922999999999999</v>
+      </c>
+      <c r="F102" s="9">
+        <f>PRODUCT(E$2:$E101)</f>
+        <v>1.8460015321972559E-2</v>
+      </c>
+      <c r="G102" s="2">
         <v>4175</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>2.2616900000000002</v>
       </c>
-      <c r="F102" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I102" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>0</v>
       </c>
@@ -2939,20 +4182,31 @@
       <c r="C103" s="3">
         <v>3.0400000000000002E-3</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="3">
+        <f t="shared" si="2"/>
+        <v>8.0196127944002669</v>
+      </c>
+      <c r="E103" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99695999999999996</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103" s="2">
         <v>99727</v>
       </c>
-      <c r="E103" s="3">
+      <c r="H103" s="3">
         <v>85.104699999999994</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I103" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>1</v>
       </c>
@@ -2962,20 +4216,32 @@
       <c r="C104" s="3">
         <v>2.1000000000000001E-4</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="3">
+        <f t="shared" si="2"/>
+        <v>5.3471075307174685</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99978999999999996</v>
+      </c>
+      <c r="F104" s="9">
+        <f>PRODUCT($E$103:E103)</f>
+        <v>0.99695999999999996</v>
+      </c>
+      <c r="G104" s="2">
         <v>99684</v>
       </c>
-      <c r="E104" s="3">
+      <c r="H104" s="3">
         <v>84.364099999999993</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>2</v>
       </c>
@@ -2985,20 +4251,32 @@
       <c r="C105" s="3">
         <v>1.1E-4</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="3">
+        <f t="shared" si="2"/>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99988999999999995</v>
+      </c>
+      <c r="F105" s="9">
+        <f>PRODUCT($E$103:E104)</f>
+        <v>0.99675063839999989</v>
+      </c>
+      <c r="G105" s="2">
         <v>99669</v>
       </c>
-      <c r="E105" s="3">
+      <c r="H105" s="3">
         <v>83.381309999999999</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>3</v>
       </c>
@@ -3008,20 +4286,32 @@
       <c r="C106" s="3">
         <v>1E-4</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="3">
+        <f t="shared" si="2"/>
+        <v>4.6051701859880918</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="F106" s="9">
+        <f>PRODUCT($E$103:E105)</f>
+        <v>0.99664099582977583</v>
+      </c>
+      <c r="G106" s="2">
         <v>99659</v>
       </c>
-      <c r="E106" s="3">
+      <c r="H106" s="3">
         <v>82.390640000000005</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J106" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>4</v>
       </c>
@@ -3031,20 +4321,32 @@
       <c r="C107" s="3">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="3">
+        <f t="shared" si="2"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="E107" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99990999999999997</v>
+      </c>
+      <c r="F107" s="9">
+        <f>PRODUCT($E$103:E106)</f>
+        <v>0.99654133173019288</v>
+      </c>
+      <c r="G107" s="2">
         <v>99650</v>
       </c>
-      <c r="E107" s="3">
+      <c r="H107" s="3">
         <v>81.398769999999999</v>
       </c>
-      <c r="F107" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G107" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I107" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>5</v>
       </c>
@@ -3054,20 +4356,32 @@
       <c r="C108" s="3">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="3">
+        <f t="shared" si="2"/>
+        <v>4.3820266346738812</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99992000000000003</v>
+      </c>
+      <c r="F108" s="9">
+        <f>PRODUCT($E$103:E107)</f>
+        <v>0.99645164301033717</v>
+      </c>
+      <c r="G108" s="2">
         <v>99642</v>
       </c>
-      <c r="E108" s="3">
+      <c r="H108" s="3">
         <v>80.405860000000004</v>
       </c>
-      <c r="F108" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J108" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>6</v>
       </c>
@@ -3077,20 +4391,32 @@
       <c r="C109" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2484952420493594</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99992999999999999</v>
+      </c>
+      <c r="F109" s="9">
+        <f>PRODUCT($E$103:E108)</f>
+        <v>0.99637192687889642</v>
+      </c>
+      <c r="G109" s="2">
         <v>99634</v>
       </c>
-      <c r="E109" s="3">
+      <c r="H109" s="3">
         <v>79.412099999999995</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G109" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I109" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>7</v>
       </c>
@@ -3100,20 +4426,32 @@
       <c r="C110" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2484952420493594</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99992999999999999</v>
+      </c>
+      <c r="F110" s="9">
+        <f>PRODUCT($E$103:E109)</f>
+        <v>0.9963021808440149</v>
+      </c>
+      <c r="G110" s="2">
         <v>99627</v>
       </c>
-      <c r="E110" s="3">
+      <c r="H110" s="3">
         <v>78.417680000000004</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I110" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J110" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>8</v>
       </c>
@@ -3123,20 +4461,32 @@
       <c r="C111" s="3">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="3">
+        <f t="shared" si="2"/>
+        <v>4.0943445622221004</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99994000000000005</v>
+      </c>
+      <c r="F111" s="9">
+        <f>PRODUCT($E$103:E110)</f>
+        <v>0.99623243969135578</v>
+      </c>
+      <c r="G111" s="2">
         <v>99621</v>
       </c>
-      <c r="E111" s="3">
+      <c r="H111" s="3">
         <v>77.422749999999994</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I111" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J111" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>9</v>
       </c>
@@ -3146,20 +4496,32 @@
       <c r="C112" s="3">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="3">
+        <f t="shared" si="2"/>
+        <v>4.0943445622221004</v>
+      </c>
+      <c r="E112" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99994000000000005</v>
+      </c>
+      <c r="F112" s="9">
+        <f>PRODUCT($E$103:E111)</f>
+        <v>0.99617266574497432</v>
+      </c>
+      <c r="G112" s="2">
         <v>99615</v>
       </c>
-      <c r="E112" s="3">
+      <c r="H112" s="3">
         <v>76.427480000000003</v>
       </c>
-      <c r="F112" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I112" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>10</v>
       </c>
@@ -3169,20 +4531,32 @@
       <c r="C113" s="3">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="3">
+        <f t="shared" si="2"/>
+        <v>4.0943445622221004</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99994000000000005</v>
+      </c>
+      <c r="F113" s="9">
+        <f>PRODUCT($E$103:E112)</f>
+        <v>0.99611289538502967</v>
+      </c>
+      <c r="G113" s="2">
         <v>99609</v>
       </c>
-      <c r="E113" s="3">
+      <c r="H113" s="3">
         <v>75.432019999999994</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G113" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I113" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>11</v>
       </c>
@@ -3192,20 +4566,32 @@
       <c r="C114" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2484952420493594</v>
+      </c>
+      <c r="E114" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99992999999999999</v>
+      </c>
+      <c r="F114" s="9">
+        <f>PRODUCT($E$103:E113)</f>
+        <v>0.99605312861130657</v>
+      </c>
+      <c r="G114" s="2">
         <v>99603</v>
       </c>
-      <c r="E114" s="3">
+      <c r="H114" s="3">
         <v>74.43656</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I114" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>12</v>
       </c>
@@ -3215,20 +4601,32 @@
       <c r="C115" s="3">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2484952420493594</v>
+      </c>
+      <c r="E115" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99992999999999999</v>
+      </c>
+      <c r="F115" s="9">
+        <f>PRODUCT($E$103:E114)</f>
+        <v>0.99598340489230375</v>
+      </c>
+      <c r="G115" s="2">
         <v>99596</v>
       </c>
-      <c r="E115" s="3">
+      <c r="H115" s="3">
         <v>73.441379999999995</v>
       </c>
-      <c r="F115" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G115" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I115" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>13</v>
       </c>
@@ -3238,20 +4636,32 @@
       <c r="C116" s="3">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="3">
+        <f t="shared" si="2"/>
+        <v>4.499809670330265</v>
+      </c>
+      <c r="E116" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99990999999999997</v>
+      </c>
+      <c r="F116" s="9">
+        <f>PRODUCT($E$103:E115)</f>
+        <v>0.99591368605396124</v>
+      </c>
+      <c r="G116" s="2">
         <v>99588</v>
       </c>
-      <c r="E116" s="3">
+      <c r="H116" s="3">
         <v>72.446780000000004</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I116" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>14</v>
       </c>
@@ -3261,20 +4671,32 @@
       <c r="C117" s="3">
         <v>1.1E-4</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="3">
+        <f t="shared" si="2"/>
+        <v>4.7004803657924166</v>
+      </c>
+      <c r="E117" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99988999999999995</v>
+      </c>
+      <c r="F117" s="9">
+        <f>PRODUCT($E$103:E116)</f>
+        <v>0.99582405382221639</v>
+      </c>
+      <c r="G117" s="2">
         <v>99578</v>
       </c>
-      <c r="E117" s="3">
+      <c r="H117" s="3">
         <v>71.453190000000006</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I117" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>15</v>
       </c>
@@ -3284,20 +4706,32 @@
       <c r="C118" s="3">
         <v>1.2999999999999999E-4</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="3">
+        <f t="shared" si="2"/>
+        <v>4.8675344504555822</v>
+      </c>
+      <c r="E118" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99987000000000004</v>
+      </c>
+      <c r="F118" s="9">
+        <f>PRODUCT($E$103:E117)</f>
+        <v>0.99571451317629589</v>
+      </c>
+      <c r="G118" s="2">
         <v>99566</v>
       </c>
-      <c r="E118" s="3">
+      <c r="H118" s="3">
         <v>70.460819999999998</v>
       </c>
-      <c r="F118" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G118" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I118" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J118" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>16</v>
       </c>
@@ -3307,20 +4741,32 @@
       <c r="C119" s="3">
         <v>1.4999999999999999E-4</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="3">
+        <f t="shared" si="2"/>
+        <v>5.0106352940962555</v>
+      </c>
+      <c r="E119" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99985000000000002</v>
+      </c>
+      <c r="F119" s="9">
+        <f>PRODUCT($E$103:E118)</f>
+        <v>0.99558507028958299</v>
+      </c>
+      <c r="G119" s="2">
         <v>99553</v>
       </c>
-      <c r="E119" s="3">
+      <c r="H119" s="3">
         <v>69.469700000000003</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I119" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>17</v>
       </c>
@@ -3330,20 +4776,32 @@
       <c r="C120" s="3">
         <v>1.7000000000000001E-4</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="3">
+        <f t="shared" si="2"/>
+        <v>5.1357984370502621</v>
+      </c>
+      <c r="E120" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99983</v>
+      </c>
+      <c r="F120" s="9">
+        <f>PRODUCT($E$103:E119)</f>
+        <v>0.99543573252903961</v>
+      </c>
+      <c r="G120" s="2">
         <v>99537</v>
       </c>
-      <c r="E120" s="3">
+      <c r="H120" s="3">
         <v>68.479799999999997</v>
       </c>
-      <c r="F120" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I120" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J120" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>18</v>
       </c>
@@ -3353,20 +4811,32 @@
       <c r="C121" s="3">
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="3">
+        <f t="shared" si="2"/>
+        <v>5.2470240721604862</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99980999999999998</v>
+      </c>
+      <c r="F121" s="9">
+        <f>PRODUCT($E$103:E120)</f>
+        <v>0.9952665084545097</v>
+      </c>
+      <c r="G121" s="2">
         <v>99519</v>
       </c>
-      <c r="E121" s="3">
+      <c r="H121" s="3">
         <v>67.491200000000006</v>
       </c>
-      <c r="F121" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I121" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>19</v>
       </c>
@@ -3376,20 +4846,32 @@
       <c r="C122" s="3">
         <v>2.1000000000000001E-4</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="3">
+        <f t="shared" si="2"/>
+        <v>5.3471075307174685</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99978999999999996</v>
+      </c>
+      <c r="F122" s="9">
+        <f>PRODUCT($E$103:E121)</f>
+        <v>0.99507740781790333</v>
+      </c>
+      <c r="G122" s="2">
         <v>99499</v>
       </c>
-      <c r="E122" s="3">
+      <c r="H122" s="3">
         <v>66.503919999999994</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I122" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J122" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>20</v>
       </c>
@@ -3399,20 +4881,32 @@
       <c r="C123" s="3">
         <v>2.3000000000000001E-4</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="3">
+        <f t="shared" si="2"/>
+        <v>5.4380793089231956</v>
+      </c>
+      <c r="E123" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99977000000000005</v>
+      </c>
+      <c r="F123" s="9">
+        <f>PRODUCT($E$103:E122)</f>
+        <v>0.99486844156226151</v>
+      </c>
+      <c r="G123" s="2">
         <v>99478</v>
       </c>
-      <c r="E123" s="3">
+      <c r="H123" s="3">
         <v>65.51782</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I123" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J123" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>21</v>
       </c>
@@ -3422,20 +4916,32 @@
       <c r="C124" s="3">
         <v>2.4000000000000001E-4</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="3">
+        <f t="shared" si="2"/>
+        <v>5.4806389233419912</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99975999999999998</v>
+      </c>
+      <c r="F124" s="9">
+        <f>PRODUCT($E$103:E123)</f>
+        <v>0.9946396218207022</v>
+      </c>
+      <c r="G124" s="2">
         <v>99454</v>
       </c>
-      <c r="E124" s="3">
+      <c r="H124" s="3">
         <v>64.532589999999999</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I124" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J124" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>22</v>
       </c>
@@ -3445,20 +4951,32 @@
       <c r="C125" s="3">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="3">
+        <f t="shared" si="2"/>
+        <v>5.521460917862246</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99975000000000003</v>
+      </c>
+      <c r="F125" s="9">
+        <f>PRODUCT($E$103:E124)</f>
+        <v>0.99440090831146521</v>
+      </c>
+      <c r="G125" s="2">
         <v>99430</v>
       </c>
-      <c r="E125" s="3">
+      <c r="H125" s="3">
         <v>63.547870000000003</v>
       </c>
-      <c r="F125" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I125" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J125" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>23</v>
       </c>
@@ -3468,20 +4986,32 @@
       <c r="C126" s="3">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="3">
+        <f t="shared" si="2"/>
+        <v>5.521460917862246</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99975000000000003</v>
+      </c>
+      <c r="F126" s="9">
+        <f>PRODUCT($E$103:E125)</f>
+        <v>0.99415230808438737</v>
+      </c>
+      <c r="G126" s="2">
         <v>99406</v>
       </c>
-      <c r="E126" s="3">
+      <c r="H126" s="3">
         <v>62.563389999999998</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I126" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>24</v>
       </c>
@@ -3491,20 +5021,32 @@
       <c r="C127" s="3">
         <v>2.5999999999999998E-4</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="3">
+        <f t="shared" si="2"/>
+        <v>5.5606816310155276</v>
+      </c>
+      <c r="E127" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99973999999999996</v>
+      </c>
+      <c r="F127" s="9">
+        <f>PRODUCT($E$103:E126)</f>
+        <v>0.99390377000736629</v>
+      </c>
+      <c r="G127" s="2">
         <v>99380</v>
       </c>
-      <c r="E127" s="3">
+      <c r="H127" s="3">
         <v>61.579000000000001</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J127" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>25</v>
       </c>
@@ -3514,20 +5056,32 @@
       <c r="C128" s="3">
         <v>2.5999999999999998E-4</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="3">
+        <f t="shared" si="2"/>
+        <v>5.5606816310155276</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99973999999999996</v>
+      </c>
+      <c r="F128" s="9">
+        <f>PRODUCT($E$103:E127)</f>
+        <v>0.99364535502716433</v>
+      </c>
+      <c r="G128" s="2">
         <v>99355</v>
       </c>
-      <c r="E128" s="3">
+      <c r="H128" s="3">
         <v>60.594630000000002</v>
       </c>
-      <c r="F128" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I128" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>26</v>
       </c>
@@ -3537,20 +5091,32 @@
       <c r="C129" s="3">
         <v>2.7E-4</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="3">
+        <f t="shared" si="2"/>
+        <v>5.598421958998375</v>
+      </c>
+      <c r="E129" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99973000000000001</v>
+      </c>
+      <c r="F129" s="9">
+        <f>PRODUCT($E$103:E128)</f>
+        <v>0.99338700723485729</v>
+      </c>
+      <c r="G129" s="2">
         <v>99328</v>
       </c>
-      <c r="E129" s="3">
+      <c r="H129" s="3">
         <v>59.610280000000003</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G129" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I129" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J129" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>27</v>
       </c>
@@ -3560,20 +5126,32 @@
       <c r="C130" s="3">
         <v>2.9E-4</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="3">
+        <f t="shared" si="2"/>
+        <v>5.6698809229805196</v>
+      </c>
+      <c r="E130" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99970999999999999</v>
+      </c>
+      <c r="F130" s="9">
+        <f>PRODUCT($E$103:E129)</f>
+        <v>0.99311879274290393</v>
+      </c>
+      <c r="G130" s="2">
         <v>99301</v>
       </c>
-      <c r="E130" s="3">
+      <c r="H130" s="3">
         <v>58.626179999999998</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I130" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>28</v>
       </c>
@@ -3583,20 +5161,32 @@
       <c r="C131" s="3">
         <v>3.1E-4</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="3">
+        <f t="shared" ref="D131:D194" si="4">LN(10^6*C131)</f>
+        <v>5.7365722974791922</v>
+      </c>
+      <c r="E131" s="3">
+        <f t="shared" si="3"/>
+        <v>0.99968999999999997</v>
+      </c>
+      <c r="F131" s="9">
+        <f>PRODUCT($E$103:E130)</f>
+        <v>0.99283078829300853</v>
+      </c>
+      <c r="G131" s="2">
         <v>99272</v>
       </c>
-      <c r="E131" s="3">
+      <c r="H131" s="3">
         <v>57.642760000000003</v>
       </c>
-      <c r="F131" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I131" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>29</v>
       </c>
@@ -3606,20 +5196,32 @@
       <c r="C132" s="3">
         <v>3.2000000000000003E-4</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="3">
+        <f t="shared" si="4"/>
+        <v>5.768320995793772</v>
+      </c>
+      <c r="E132" s="3">
+        <f t="shared" ref="E132:E195" si="5">1-C132</f>
+        <v>0.99968000000000001</v>
+      </c>
+      <c r="F132" s="9">
+        <f>PRODUCT($E$103:E131)</f>
+        <v>0.99252301074863769</v>
+      </c>
+      <c r="G132" s="2">
         <v>99240</v>
       </c>
-      <c r="E132" s="3">
+      <c r="H132" s="3">
         <v>56.660200000000003</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I132" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>30</v>
       </c>
@@ -3629,20 +5231,32 @@
       <c r="C133" s="3">
         <v>3.4000000000000002E-4</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="3">
+        <f t="shared" si="4"/>
+        <v>5.8289456176102075</v>
+      </c>
+      <c r="E133" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99965999999999999</v>
+      </c>
+      <c r="F133" s="9">
+        <f>PRODUCT($E$103:E132)</f>
+        <v>0.99220540338519814</v>
+      </c>
+      <c r="G133" s="2">
         <v>99207</v>
       </c>
-      <c r="E133" s="3">
+      <c r="H133" s="3">
         <v>55.678429999999999</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G133" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I133" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>31</v>
       </c>
@@ -3652,20 +5266,32 @@
       <c r="C134" s="3">
         <v>3.6000000000000002E-4</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="3">
+        <f t="shared" si="4"/>
+        <v>5.8861040314501558</v>
+      </c>
+      <c r="E134" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99963999999999997</v>
+      </c>
+      <c r="F134" s="9">
+        <f>PRODUCT($E$103:E133)</f>
+        <v>0.99186805354804719</v>
+      </c>
+      <c r="G134" s="2">
         <v>99173</v>
       </c>
-      <c r="E134" s="3">
+      <c r="H134" s="3">
         <v>54.697319999999998</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G134" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I134" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>32</v>
       </c>
@@ -3675,20 +5301,32 @@
       <c r="C135" s="3">
         <v>3.8000000000000002E-4</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="3">
+        <f t="shared" si="4"/>
+        <v>5.9401712527204316</v>
+      </c>
+      <c r="E135" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99961999999999995</v>
+      </c>
+      <c r="F135" s="9">
+        <f>PRODUCT($E$103:E134)</f>
+        <v>0.99151098104876989</v>
+      </c>
+      <c r="G135" s="2">
         <v>99136</v>
       </c>
-      <c r="E135" s="3">
+      <c r="H135" s="3">
         <v>53.716700000000003</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I135" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J135" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>33</v>
       </c>
@@ -3698,20 +5336,32 @@
       <c r="C136" s="3">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="3">
+        <f t="shared" si="4"/>
+        <v>5.9914645471079817</v>
+      </c>
+      <c r="E136" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99960000000000004</v>
+      </c>
+      <c r="F136" s="9">
+        <f>PRODUCT($E$103:E135)</f>
+        <v>0.99113420687597131</v>
+      </c>
+      <c r="G136" s="2">
         <v>99098</v>
       </c>
-      <c r="E136" s="3">
+      <c r="H136" s="3">
         <v>52.736699999999999</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G136" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I136" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J136" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>34</v>
       </c>
@@ -3721,20 +5371,32 @@
       <c r="C137" s="3">
         <v>4.2000000000000002E-4</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="3">
+        <f t="shared" si="4"/>
+        <v>6.0402547112774139</v>
+      </c>
+      <c r="E137" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99958000000000002</v>
+      </c>
+      <c r="F137" s="9">
+        <f>PRODUCT($E$103:E136)</f>
+        <v>0.99073775319322099</v>
+      </c>
+      <c r="G137" s="2">
         <v>99058</v>
       </c>
-      <c r="E137" s="3">
+      <c r="H137" s="3">
         <v>51.757399999999997</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G137" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I137" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J137" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>35</v>
       </c>
@@ -3744,20 +5406,32 @@
       <c r="C138" s="3">
         <v>4.4999999999999999E-4</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="3">
+        <f t="shared" si="4"/>
+        <v>6.1092475827643655</v>
+      </c>
+      <c r="E138" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99955000000000005</v>
+      </c>
+      <c r="F138" s="9">
+        <f>PRODUCT($E$103:E137)</f>
+        <v>0.99032164333687989</v>
+      </c>
+      <c r="G138" s="2">
         <v>99014</v>
       </c>
-      <c r="E138" s="3">
+      <c r="H138" s="3">
         <v>50.779069999999997</v>
       </c>
-      <c r="F138" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I138" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>36</v>
       </c>
@@ -3767,20 +5441,32 @@
       <c r="C139" s="3">
         <v>4.8999999999999998E-4</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="3">
+        <f t="shared" si="4"/>
+        <v>6.1944053911046719</v>
+      </c>
+      <c r="E139" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99951000000000001</v>
+      </c>
+      <c r="F139" s="9">
+        <f>PRODUCT($E$103:E138)</f>
+        <v>0.98987599859737829</v>
+      </c>
+      <c r="G139" s="2">
         <v>98968</v>
       </c>
-      <c r="E139" s="3">
+      <c r="H139" s="3">
         <v>49.801859999999998</v>
       </c>
-      <c r="F139" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I139" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J139" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>37</v>
       </c>
@@ -3790,20 +5476,32 @@
       <c r="C140" s="3">
         <v>5.2999999999999998E-4</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="3">
+        <f t="shared" si="4"/>
+        <v>6.2728770065461674</v>
+      </c>
+      <c r="E140" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99946999999999997</v>
+      </c>
+      <c r="F140" s="9">
+        <f>PRODUCT($E$103:E139)</f>
+        <v>0.98939095935806554</v>
+      </c>
+      <c r="G140" s="2">
         <v>98917</v>
       </c>
-      <c r="E140" s="3">
+      <c r="H140" s="3">
         <v>48.825989999999997</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I140" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>38</v>
       </c>
@@ -3813,20 +5511,32 @@
       <c r="C141" s="3">
         <v>5.9000000000000003E-4</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="3">
+        <f t="shared" si="4"/>
+        <v>6.3801225368997647</v>
+      </c>
+      <c r="E141" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99941000000000002</v>
+      </c>
+      <c r="F141" s="9">
+        <f>PRODUCT($E$103:E140)</f>
+        <v>0.98886658214960577</v>
+      </c>
+      <c r="G141" s="2">
         <v>98862</v>
       </c>
-      <c r="E141" s="3">
+      <c r="H141" s="3">
         <v>47.851779999999998</v>
       </c>
-      <c r="F141" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G141" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I141" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J141" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>39</v>
       </c>
@@ -3836,20 +5546,32 @@
       <c r="C142" s="3">
         <v>6.4999999999999997E-4</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="3">
+        <f t="shared" si="4"/>
+        <v>6.4769723628896827</v>
+      </c>
+      <c r="E142" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99934999999999996</v>
+      </c>
+      <c r="F142" s="9">
+        <f>PRODUCT($E$103:E141)</f>
+        <v>0.98828315086613749</v>
+      </c>
+      <c r="G142" s="2">
         <v>98800</v>
       </c>
-      <c r="E142" s="3">
+      <c r="H142" s="3">
         <v>46.879689999999997</v>
       </c>
-      <c r="F142" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I142" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J142" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>40</v>
       </c>
@@ -3859,20 +5581,32 @@
       <c r="C143" s="3">
         <v>7.2000000000000005E-4</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="3">
+        <f t="shared" si="4"/>
+        <v>6.5792512120101012</v>
+      </c>
+      <c r="E143" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99927999999999995</v>
+      </c>
+      <c r="F143" s="9">
+        <f>PRODUCT($E$103:E142)</f>
+        <v>0.98764076681807444</v>
+      </c>
+      <c r="G143" s="2">
         <v>98733</v>
       </c>
-      <c r="E143" s="3">
+      <c r="H143" s="3">
         <v>45.909950000000002</v>
       </c>
-      <c r="F143" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I143" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>41</v>
       </c>
@@ -3882,20 +5616,32 @@
       <c r="C144" s="3">
         <v>7.7999999999999999E-4</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="3">
+        <f t="shared" si="4"/>
+        <v>6.6592939196836376</v>
+      </c>
+      <c r="E144" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99922</v>
+      </c>
+      <c r="F144" s="9">
+        <f>PRODUCT($E$103:E143)</f>
+        <v>0.98692966546596539</v>
+      </c>
+      <c r="G144" s="2">
         <v>98659</v>
       </c>
-      <c r="E144" s="3">
+      <c r="H144" s="3">
         <v>44.942520000000002</v>
       </c>
-      <c r="F144" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I144" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J144" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>42</v>
       </c>
@@ -3905,20 +5651,32 @@
       <c r="C145" s="3">
         <v>8.5999999999999998E-4</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="3">
+        <f t="shared" si="4"/>
+        <v>6.7569323892475532</v>
+      </c>
+      <c r="E145" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99914000000000003</v>
+      </c>
+      <c r="F145" s="9">
+        <f>PRODUCT($E$103:E144)</f>
+        <v>0.98615986032690195</v>
+      </c>
+      <c r="G145" s="2">
         <v>98578</v>
       </c>
-      <c r="E145" s="3">
+      <c r="H145" s="3">
         <v>43.977359999999997</v>
       </c>
-      <c r="F145" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I145" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J145" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>43</v>
       </c>
@@ -3928,20 +5686,32 @@
       <c r="C146" s="3">
         <v>9.3999999999999997E-4</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="3">
+        <f t="shared" si="4"/>
+        <v>6.8458798752640497</v>
+      </c>
+      <c r="E146" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99905999999999995</v>
+      </c>
+      <c r="F146" s="9">
+        <f>PRODUCT($E$103:E145)</f>
+        <v>0.98531176284702082</v>
+      </c>
+      <c r="G146" s="2">
         <v>98489</v>
       </c>
-      <c r="E146" s="3">
+      <c r="H146" s="3">
         <v>43.014679999999998</v>
       </c>
-      <c r="F146" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I146" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>44</v>
       </c>
@@ -3951,20 +5721,32 @@
       <c r="C147" s="3">
         <v>1.0300000000000001E-3</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="3">
+        <f t="shared" si="4"/>
+        <v>6.9373140812236818</v>
+      </c>
+      <c r="E147" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99897000000000002</v>
+      </c>
+      <c r="F147" s="9">
+        <f>PRODUCT($E$103:E146)</f>
+        <v>0.98438556978994463</v>
+      </c>
+      <c r="G147" s="2">
         <v>98392</v>
       </c>
-      <c r="E147" s="3">
+      <c r="H147" s="3">
         <v>42.054789999999997</v>
       </c>
-      <c r="F147" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G147" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I147" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J147" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45</v>
       </c>
@@ -3974,20 +5756,32 @@
       <c r="C148" s="3">
         <v>1.1199999999999999E-3</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="3">
+        <f t="shared" si="4"/>
+        <v>7.0210839642891401</v>
+      </c>
+      <c r="E148" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99887999999999999</v>
+      </c>
+      <c r="F148" s="9">
+        <f>PRODUCT($E$103:E147)</f>
+        <v>0.98337165265306103</v>
+      </c>
+      <c r="G148" s="2">
         <v>98286</v>
       </c>
-      <c r="E148" s="3">
+      <c r="H148" s="3">
         <v>41.097679999999997</v>
       </c>
-      <c r="F148" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I148" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J148" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46</v>
       </c>
@@ -3997,20 +5791,32 @@
       <c r="C149" s="3">
         <v>1.2099999999999999E-3</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="3">
+        <f t="shared" si="4"/>
+        <v>7.0983756385907864</v>
+      </c>
+      <c r="E149" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99878999999999996</v>
+      </c>
+      <c r="F149" s="9">
+        <f>PRODUCT($E$103:E148)</f>
+        <v>0.98227027640208964</v>
+      </c>
+      <c r="G149" s="2">
         <v>98172</v>
       </c>
-      <c r="E149" s="3">
+      <c r="H149" s="3">
         <v>40.143099999999997</v>
       </c>
-      <c r="F149" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G149" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I149" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J149" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>47</v>
       </c>
@@ -4020,20 +5826,32 @@
       <c r="C150" s="3">
         <v>1.32E-3</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="3">
+        <f t="shared" si="4"/>
+        <v>7.1853870155804165</v>
+      </c>
+      <c r="E150" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99868000000000001</v>
+      </c>
+      <c r="F150" s="9">
+        <f>PRODUCT($E$103:E149)</f>
+        <v>0.98108172936764304</v>
+      </c>
+      <c r="G150" s="2">
         <v>98047</v>
       </c>
-      <c r="E150" s="3">
+      <c r="H150" s="3">
         <v>39.191290000000002</v>
       </c>
-      <c r="F150" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I150" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>48</v>
       </c>
@@ -4043,20 +5861,32 @@
       <c r="C151" s="3">
         <v>1.4499999999999999E-3</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="3">
+        <f t="shared" si="4"/>
+        <v>7.2793188354146201</v>
+      </c>
+      <c r="E151" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99855000000000005</v>
+      </c>
+      <c r="F151" s="9">
+        <f>PRODUCT($E$103:E150)</f>
+        <v>0.97978670148487779</v>
+      </c>
+      <c r="G151" s="2">
         <v>97912</v>
       </c>
-      <c r="E151" s="3">
+      <c r="H151" s="3">
         <v>38.242460000000001</v>
       </c>
-      <c r="F151" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G151" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I151" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J151" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>49</v>
       </c>
@@ -4066,20 +5896,32 @@
       <c r="C152" s="3">
         <v>1.58E-3</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="3">
+        <f t="shared" si="4"/>
+        <v>7.3651801260210128</v>
+      </c>
+      <c r="E152" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99841999999999997</v>
+      </c>
+      <c r="F152" s="9">
+        <f>PRODUCT($E$103:E151)</f>
+        <v>0.97836601076772478</v>
+      </c>
+      <c r="G152" s="2">
         <v>97764</v>
       </c>
-      <c r="E152" s="3">
+      <c r="H152" s="3">
         <v>37.2971</v>
       </c>
-      <c r="F152" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I152" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J152" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>50</v>
       </c>
@@ -4089,20 +5931,32 @@
       <c r="C153" s="3">
         <v>1.73E-3</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="3">
+        <f t="shared" si="4"/>
+        <v>7.4558766874918243</v>
+      </c>
+      <c r="E153" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99826999999999999</v>
+      </c>
+      <c r="F153" s="9">
+        <f>PRODUCT($E$103:E152)</f>
+        <v>0.97682019247071172</v>
+      </c>
+      <c r="G153" s="2">
         <v>97602</v>
       </c>
-      <c r="E153" s="3">
+      <c r="H153" s="3">
         <v>36.355429999999998</v>
       </c>
-      <c r="F153" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G153" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J153" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>51</v>
       </c>
@@ -4112,20 +5966,32 @@
       <c r="C154" s="3">
         <v>1.9E-3</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="3">
+        <f t="shared" si="4"/>
+        <v>7.5496091651545321</v>
+      </c>
+      <c r="E154" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99809999999999999</v>
+      </c>
+      <c r="F154" s="9">
+        <f>PRODUCT($E$103:E153)</f>
+        <v>0.97513029353773739</v>
+      </c>
+      <c r="G154" s="2">
         <v>97424</v>
       </c>
-      <c r="E154" s="3">
+      <c r="H154" s="3">
         <v>35.41771</v>
       </c>
-      <c r="F154" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I154" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J154" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>52</v>
       </c>
@@ -4135,20 +6001,32 @@
       <c r="C155" s="3">
         <v>2.0699999999999998E-3</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="3">
+        <f t="shared" si="4"/>
+        <v>7.6353038862594147</v>
+      </c>
+      <c r="E155" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99792999999999998</v>
+      </c>
+      <c r="F155" s="9">
+        <f>PRODUCT($E$103:E154)</f>
+        <v>0.9732775459800157</v>
+      </c>
+      <c r="G155" s="2">
         <v>97231</v>
       </c>
-      <c r="E155" s="3">
+      <c r="H155" s="3">
         <v>34.484160000000003</v>
       </c>
-      <c r="F155" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G155" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I155" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J155" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>53</v>
       </c>
@@ -4158,20 +6036,32 @@
       <c r="C156" s="3">
         <v>2.2499999999999998E-3</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="3">
+        <f t="shared" si="4"/>
+        <v>7.718685495198466</v>
+      </c>
+      <c r="E156" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99775000000000003</v>
+      </c>
+      <c r="F156" s="9">
+        <f>PRODUCT($E$103:E155)</f>
+        <v>0.97126286145983709</v>
+      </c>
+      <c r="G156" s="2">
         <v>97021</v>
       </c>
-      <c r="E156" s="3">
+      <c r="H156" s="3">
         <v>33.554749999999999</v>
       </c>
-      <c r="F156" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I156" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J156" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>54</v>
       </c>
@@ -4181,20 +6071,32 @@
       <c r="C157" s="3">
         <v>2.4299999999999999E-3</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="3">
+        <f t="shared" si="4"/>
+        <v>7.7956465363345941</v>
+      </c>
+      <c r="E157" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99756999999999996</v>
+      </c>
+      <c r="F157" s="9">
+        <f>PRODUCT($E$103:E156)</f>
+        <v>0.96907752002155245</v>
+      </c>
+      <c r="G157" s="2">
         <v>96793</v>
       </c>
-      <c r="E157" s="3">
+      <c r="H157" s="3">
         <v>32.629420000000003</v>
       </c>
-      <c r="F157" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G157" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I157" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J157" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>55</v>
       </c>
@@ -4204,20 +6106,32 @@
       <c r="C158" s="3">
         <v>2.6099999999999999E-3</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="3">
+        <f t="shared" si="4"/>
+        <v>7.8671055003167387</v>
+      </c>
+      <c r="E158" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99739</v>
+      </c>
+      <c r="F158" s="9">
+        <f>PRODUCT($E$103:E157)</f>
+        <v>0.96672266164789999</v>
+      </c>
+      <c r="G158" s="2">
         <v>96549</v>
       </c>
-      <c r="E158" s="3">
+      <c r="H158" s="3">
         <v>31.707789999999999</v>
       </c>
-      <c r="F158" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I158" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J158" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>56</v>
       </c>
@@ -4227,20 +6141,32 @@
       <c r="C159" s="3">
         <v>2.81E-3</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="3">
+        <f t="shared" si="4"/>
+        <v>7.9409397623277913</v>
+      </c>
+      <c r="E159" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99719000000000002</v>
+      </c>
+      <c r="F159" s="9">
+        <f>PRODUCT($E$103:E158)</f>
+        <v>0.96419951550099903</v>
+      </c>
+      <c r="G159" s="2">
         <v>96288</v>
       </c>
-      <c r="E159" s="3">
+      <c r="H159" s="3">
         <v>30.789529999999999</v>
       </c>
-      <c r="F159" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I159" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J159" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>57</v>
       </c>
@@ -4250,20 +6176,32 @@
       <c r="C160" s="3">
         <v>3.0200000000000001E-3</v>
       </c>
-      <c r="D160" s="2">
+      <c r="D160" s="3">
+        <f t="shared" si="4"/>
+        <v>8.0130121103689156</v>
+      </c>
+      <c r="E160" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99697999999999998</v>
+      </c>
+      <c r="F160" s="9">
+        <f>PRODUCT($E$103:E159)</f>
+        <v>0.96149011486244129</v>
+      </c>
+      <c r="G160" s="2">
         <v>96007</v>
       </c>
-      <c r="E160" s="3">
+      <c r="H160" s="3">
         <v>29.87473</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I160" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>58</v>
       </c>
@@ -4273,20 +6211,32 @@
       <c r="C161" s="3">
         <v>3.2599999999999999E-3</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="3">
+        <f t="shared" si="4"/>
+        <v>8.0894824743607536</v>
+      </c>
+      <c r="E161" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99673999999999996</v>
+      </c>
+      <c r="F161" s="9">
+        <f>PRODUCT($E$103:E160)</f>
+        <v>0.95858641471555672</v>
+      </c>
+      <c r="G161" s="2">
         <v>95706</v>
       </c>
-      <c r="E161" s="3">
+      <c r="H161" s="3">
         <v>28.963660000000001</v>
       </c>
-      <c r="F161" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I161" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>59</v>
       </c>
@@ -4296,20 +6246,32 @@
       <c r="C162" s="3">
         <v>3.5200000000000001E-3</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="3">
+        <f t="shared" si="4"/>
+        <v>8.1662162685921427</v>
+      </c>
+      <c r="E162" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99648000000000003</v>
+      </c>
+      <c r="F162" s="9">
+        <f>PRODUCT($E$103:E161)</f>
+        <v>0.95546142300358394</v>
+      </c>
+      <c r="G162" s="2">
         <v>95382</v>
       </c>
-      <c r="E162" s="3">
+      <c r="H162" s="3">
         <v>28.056619999999999</v>
       </c>
-      <c r="F162" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G162" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I162" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>60</v>
       </c>
@@ -4319,20 +6281,32 @@
       <c r="C163" s="3">
         <v>3.81E-3</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="3">
+        <f t="shared" si="4"/>
+        <v>8.2453844681207471</v>
+      </c>
+      <c r="E163" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99619000000000002</v>
+      </c>
+      <c r="F163" s="9">
+        <f>PRODUCT($E$103:E162)</f>
+        <v>0.95209819879461133</v>
+      </c>
+      <c r="G163" s="2">
         <v>95033</v>
       </c>
-      <c r="E163" s="3">
+      <c r="H163" s="3">
         <v>27.153929999999999</v>
       </c>
-      <c r="F163" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I163" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>61</v>
       </c>
@@ -4342,20 +6316,32 @@
       <c r="C164" s="3">
         <v>4.13E-3</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="3">
+        <f t="shared" si="4"/>
+        <v>8.3260326859550791</v>
+      </c>
+      <c r="E164" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99587000000000003</v>
+      </c>
+      <c r="F164" s="9">
+        <f>PRODUCT($E$103:E163)</f>
+        <v>0.94847070465720384</v>
+      </c>
+      <c r="G164" s="2">
         <v>94656</v>
       </c>
-      <c r="E164" s="3">
+      <c r="H164" s="3">
         <v>26.255759999999999</v>
       </c>
-      <c r="F164" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G164" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I164" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>62</v>
       </c>
@@ -4365,20 +6351,32 @@
       <c r="C165" s="3">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="D165" s="2">
+      <c r="D165" s="3">
+        <f t="shared" si="4"/>
+        <v>8.4118326757584114</v>
+      </c>
+      <c r="E165" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99550000000000005</v>
+      </c>
+      <c r="F165" s="9">
+        <f>PRODUCT($E$103:E164)</f>
+        <v>0.94455352064696962</v>
+      </c>
+      <c r="G165" s="2">
         <v>94248</v>
       </c>
-      <c r="E165" s="3">
+      <c r="H165" s="3">
         <v>25.362570000000002</v>
       </c>
-      <c r="F165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G165" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I165" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J165" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>63</v>
       </c>
@@ -4388,20 +6386,32 @@
       <c r="C166" s="3">
         <v>4.9100000000000003E-3</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="3">
+        <f t="shared" si="4"/>
+        <v>8.4990292207885663</v>
+      </c>
+      <c r="E166" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99509000000000003</v>
+      </c>
+      <c r="F166" s="9">
+        <f>PRODUCT($E$103:E165)</f>
+        <v>0.94030302980405833</v>
+      </c>
+      <c r="G166" s="2">
         <v>93805</v>
       </c>
-      <c r="E166" s="3">
+      <c r="H166" s="3">
         <v>24.47486</v>
       </c>
-      <c r="F166" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G166" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I166" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J166" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>64</v>
       </c>
@@ -4411,20 +6421,32 @@
       <c r="C167" s="3">
         <v>5.3699999999999998E-3</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="3">
+        <f t="shared" si="4"/>
+        <v>8.5885831875029108</v>
+      </c>
+      <c r="E167" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99463000000000001</v>
+      </c>
+      <c r="F167" s="9">
+        <f>PRODUCT($E$103:E166)</f>
+        <v>0.93568614192772048</v>
+      </c>
+      <c r="G167" s="2">
         <v>93324</v>
       </c>
-      <c r="E167" s="3">
+      <c r="H167" s="3">
         <v>23.59308</v>
       </c>
-      <c r="F167" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G167" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I167" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J167" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>65</v>
       </c>
@@ -4434,20 +6456,32 @@
       <c r="C168" s="3">
         <v>5.8599999999999998E-3</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="3">
+        <f t="shared" si="4"/>
+        <v>8.675904882571059</v>
+      </c>
+      <c r="E168" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99414000000000002</v>
+      </c>
+      <c r="F168" s="9">
+        <f>PRODUCT($E$103:E167)</f>
+        <v>0.93066150734556863</v>
+      </c>
+      <c r="G168" s="2">
         <v>92801</v>
       </c>
-      <c r="E168" s="3">
+      <c r="H168" s="3">
         <v>22.717610000000001</v>
       </c>
-      <c r="F168" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G168" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I168" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J168" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>66</v>
       </c>
@@ -4457,20 +6491,32 @@
       <c r="C169" s="3">
         <v>6.3800000000000003E-3</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="3">
+        <f t="shared" si="4"/>
+        <v>8.7609233763388357</v>
+      </c>
+      <c r="E169" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99361999999999995</v>
+      </c>
+      <c r="F169" s="9">
+        <f>PRODUCT($E$103:E168)</f>
+        <v>0.92520783091252357</v>
+      </c>
+      <c r="G169" s="2">
         <v>92233</v>
       </c>
-      <c r="E169" s="3">
+      <c r="H169" s="3">
         <v>21.84844</v>
       </c>
-      <c r="F169" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G169" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I169" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J169" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>67</v>
       </c>
@@ -4480,20 +6526,32 @@
       <c r="C170" s="3">
         <v>6.96E-3</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="3">
+        <f t="shared" si="4"/>
+        <v>8.8479347533284649</v>
+      </c>
+      <c r="E170" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99304000000000003</v>
+      </c>
+      <c r="F170" s="9">
+        <f>PRODUCT($E$103:E169)</f>
+        <v>0.91930500495130163</v>
+      </c>
+      <c r="G170" s="2">
         <v>91618</v>
       </c>
-      <c r="E170" s="3">
+      <c r="H170" s="3">
         <v>20.98546</v>
       </c>
-      <c r="F170" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G170" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I170" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>68</v>
       </c>
@@ -4503,20 +6561,32 @@
       <c r="C171" s="3">
         <v>7.6299999999999996E-3</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="3">
+        <f t="shared" si="4"/>
+        <v>8.9398431242785019</v>
+      </c>
+      <c r="E171" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99236999999999997</v>
+      </c>
+      <c r="F171" s="9">
+        <f>PRODUCT($E$103:E170)</f>
+        <v>0.91290664211684058</v>
+      </c>
+      <c r="G171" s="2">
         <v>90951</v>
       </c>
-      <c r="E171" s="3">
+      <c r="H171" s="3">
         <v>20.129090000000001</v>
       </c>
-      <c r="F171" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G171" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I171" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J171" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>69</v>
       </c>
@@ -4526,20 +6596,32 @@
       <c r="C172" s="3">
         <v>8.3599999999999994E-3</v>
       </c>
-      <c r="D172" s="2">
+      <c r="D172" s="3">
+        <f t="shared" si="4"/>
+        <v>9.0312137060787467</v>
+      </c>
+      <c r="E172" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99163999999999997</v>
+      </c>
+      <c r="F172" s="9">
+        <f>PRODUCT($E$103:E171)</f>
+        <v>0.90594116443748907</v>
+      </c>
+      <c r="G172" s="2">
         <v>90224</v>
       </c>
-      <c r="E172" s="3">
+      <c r="H172" s="3">
         <v>19.27993</v>
       </c>
-      <c r="F172" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G172" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I172" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J172" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>70</v>
       </c>
@@ -4549,20 +6631,32 @@
       <c r="C173" s="3">
         <v>9.1599999999999997E-3</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="3">
+        <f t="shared" si="4"/>
+        <v>9.1226014576681766</v>
+      </c>
+      <c r="E173" s="3">
+        <f t="shared" si="5"/>
+        <v>0.99084000000000005</v>
+      </c>
+      <c r="F173" s="9">
+        <f>PRODUCT($E$103:E172)</f>
+        <v>0.89836749630279167</v>
+      </c>
+      <c r="G173" s="2">
         <v>89434</v>
       </c>
-      <c r="E173" s="3">
+      <c r="H173" s="3">
         <v>18.438230000000001</v>
       </c>
-      <c r="F173" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G173" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I173" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J173" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>71</v>
       </c>
@@ -4572,20 +6666,32 @@
       <c r="C174" s="3">
         <v>1.005E-2</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="3">
+        <f t="shared" si="4"/>
+        <v>9.2153279134872221</v>
+      </c>
+      <c r="E174" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98995</v>
+      </c>
+      <c r="F174" s="9">
+        <f>PRODUCT($E$103:E173)</f>
+        <v>0.89013845003665815</v>
+      </c>
+      <c r="G174" s="2">
         <v>88576</v>
       </c>
-      <c r="E174" s="3">
+      <c r="H174" s="3">
         <v>17.604050000000001</v>
       </c>
-      <c r="F174" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G174" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I174" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J174" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>72</v>
       </c>
@@ -4595,20 +6701,32 @@
       <c r="C175" s="3">
         <v>1.108E-2</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="3">
+        <f t="shared" si="4"/>
+        <v>9.3128969603012752</v>
+      </c>
+      <c r="E175" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98892000000000002</v>
+      </c>
+      <c r="F175" s="9">
+        <f>PRODUCT($E$103:E174)</f>
+        <v>0.88119255861378976</v>
+      </c>
+      <c r="G175" s="2">
         <v>87642</v>
       </c>
-      <c r="E175" s="3">
+      <c r="H175" s="3">
         <v>16.777560000000001</v>
       </c>
-      <c r="F175" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G175" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I175" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J175" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>73</v>
       </c>
@@ -4618,20 +6736,32 @@
       <c r="C176" s="3">
         <v>1.2330000000000001E-2</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="3">
+        <f t="shared" si="4"/>
+        <v>9.4197905961583892</v>
+      </c>
+      <c r="E176" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98767000000000005</v>
+      </c>
+      <c r="F176" s="9">
+        <f>PRODUCT($E$103:E175)</f>
+        <v>0.87142894506434898</v>
+      </c>
+      <c r="G176" s="2">
         <v>86618</v>
       </c>
-      <c r="E176" s="3">
+      <c r="H176" s="3">
         <v>15.95979</v>
       </c>
-      <c r="F176" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G176" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I176" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J176" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>74</v>
       </c>
@@ -4641,20 +6771,32 @@
       <c r="C177" s="3">
         <v>1.3860000000000001E-2</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="3">
+        <f t="shared" si="4"/>
+        <v>9.5367622727438945</v>
+      </c>
+      <c r="E177" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98614000000000002</v>
+      </c>
+      <c r="F177" s="9">
+        <f>PRODUCT($E$103:E176)</f>
+        <v>0.86068422617170559</v>
+      </c>
+      <c r="G177" s="2">
         <v>85486</v>
       </c>
-      <c r="E177" s="3">
+      <c r="H177" s="3">
         <v>15.152710000000001</v>
       </c>
-      <c r="F177" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G177" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I177" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J177" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>75</v>
       </c>
@@ -4664,20 +6806,32 @@
       <c r="C178" s="3">
         <v>1.5679999999999999E-2</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="3">
+        <f t="shared" si="4"/>
+        <v>9.6601412939043989</v>
+      </c>
+      <c r="E178" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98431999999999997</v>
+      </c>
+      <c r="F178" s="9">
+        <f>PRODUCT($E$103:E177)</f>
+        <v>0.84875514279696573</v>
+      </c>
+      <c r="G178" s="2">
         <v>84226</v>
       </c>
-      <c r="E178" s="3">
+      <c r="H178" s="3">
         <v>14.358499999999999</v>
       </c>
-      <c r="F178" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G178" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I178" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J178" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>76</v>
       </c>
@@ -4687,20 +6841,32 @@
       <c r="C179" s="3">
         <v>1.7809999999999999E-2</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="3">
+        <f t="shared" si="4"/>
+        <v>9.7875153762837073</v>
+      </c>
+      <c r="E179" s="3">
+        <f t="shared" si="5"/>
+        <v>0.98219000000000001</v>
+      </c>
+      <c r="F179" s="9">
+        <f>PRODUCT($E$103:E178)</f>
+        <v>0.8354466621579093</v>
+      </c>
+      <c r="G179" s="2">
         <v>82818</v>
       </c>
-      <c r="E179" s="3">
+      <c r="H179" s="3">
         <v>13.5791</v>
       </c>
-      <c r="F179" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G179" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I179" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J179" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>77</v>
       </c>
@@ -4710,20 +6876,32 @@
       <c r="C180" s="3">
         <v>2.027E-2</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="3">
+        <f t="shared" si="4"/>
+        <v>9.9168972394460457</v>
+      </c>
+      <c r="E180" s="3">
+        <f t="shared" si="5"/>
+        <v>0.97972999999999999</v>
+      </c>
+      <c r="F180" s="9">
+        <f>PRODUCT($E$103:E179)</f>
+        <v>0.82056735710487694</v>
+      </c>
+      <c r="G180" s="2">
         <v>81244</v>
       </c>
-      <c r="E180" s="3">
+      <c r="H180" s="3">
         <v>12.81611</v>
       </c>
-      <c r="F180" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G180" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I180" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J180" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>78</v>
       </c>
@@ -4733,20 +6911,32 @@
       <c r="C181" s="3">
         <v>2.308E-2</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="3">
+        <f t="shared" si="4"/>
+        <v>10.046721720622037</v>
+      </c>
+      <c r="E181" s="3">
+        <f t="shared" si="5"/>
+        <v>0.97692000000000001</v>
+      </c>
+      <c r="F181" s="9">
+        <f>PRODUCT($E$103:E180)</f>
+        <v>0.80393445677636111</v>
+      </c>
+      <c r="G181" s="2">
         <v>79486</v>
       </c>
-      <c r="E181" s="3">
+      <c r="H181" s="3">
         <v>12.070690000000001</v>
       </c>
-      <c r="F181" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I181" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J181" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>79</v>
       </c>
@@ -4756,20 +6946,32 @@
       <c r="C182" s="3">
         <v>2.63E-2</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="3">
+        <f t="shared" si="4"/>
+        <v>10.177324218165856</v>
+      </c>
+      <c r="E182" s="3">
+        <f t="shared" si="5"/>
+        <v>0.97370000000000001</v>
+      </c>
+      <c r="F182" s="9">
+        <f>PRODUCT($E$103:E181)</f>
+        <v>0.78537964951396266</v>
+      </c>
+      <c r="G182" s="2">
         <v>77527</v>
       </c>
-      <c r="E182" s="3">
+      <c r="H182" s="3">
         <v>11.34389</v>
       </c>
-      <c r="F182" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G182" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I182" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J182" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>80</v>
       </c>
@@ -4779,20 +6981,32 @@
       <c r="C183" s="3">
         <v>0.03</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="3">
+        <f t="shared" si="4"/>
+        <v>10.308952660644293</v>
+      </c>
+      <c r="E183" s="3">
+        <f t="shared" si="5"/>
+        <v>0.97</v>
+      </c>
+      <c r="F183" s="9">
+        <f>PRODUCT($E$103:E182)</f>
+        <v>0.76472416473174543</v>
+      </c>
+      <c r="G183" s="2">
         <v>75349</v>
       </c>
-      <c r="E183" s="3">
+      <c r="H183" s="3">
         <v>10.63653</v>
       </c>
-      <c r="F183" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G183" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I183" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J183" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>81</v>
       </c>
@@ -4802,20 +7016,32 @@
       <c r="C184" s="3">
         <v>3.4259999999999999E-2</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="3">
+        <f t="shared" si="4"/>
+        <v>10.441733771878111</v>
+      </c>
+      <c r="E184" s="3">
+        <f t="shared" si="5"/>
+        <v>0.96574000000000004</v>
+      </c>
+      <c r="F184" s="9">
+        <f>PRODUCT($E$103:E183)</f>
+        <v>0.74178243978979308</v>
+      </c>
+      <c r="G184" s="2">
         <v>72934</v>
       </c>
-      <c r="E184" s="3">
+      <c r="H184" s="3">
         <v>9.9497099999999996</v>
       </c>
-      <c r="F184" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G184" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I184" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J184" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>82</v>
       </c>
@@ -4825,20 +7051,32 @@
       <c r="C185" s="3">
         <v>3.9210000000000002E-2</v>
       </c>
-      <c r="D185" s="2">
+      <c r="D185" s="3">
+        <f t="shared" si="4"/>
+        <v>10.576687095286378</v>
+      </c>
+      <c r="E185" s="3">
+        <f t="shared" si="5"/>
+        <v>0.96079000000000003</v>
+      </c>
+      <c r="F185" s="9">
+        <f>PRODUCT($E$103:E184)</f>
+        <v>0.71636897340259476</v>
+      </c>
+      <c r="G185" s="2">
         <v>70260</v>
       </c>
-      <c r="E185" s="3">
+      <c r="H185" s="3">
         <v>9.2846499999999992</v>
       </c>
-      <c r="F185" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G185" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I185" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>83</v>
       </c>
@@ -4848,20 +7086,32 @@
       <c r="C186" s="3">
         <v>4.496E-2</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="3">
+        <f t="shared" si="4"/>
+        <v>10.713528484567572</v>
+      </c>
+      <c r="E186" s="3">
+        <f t="shared" si="5"/>
+        <v>0.95504</v>
+      </c>
+      <c r="F186" s="9">
+        <f>PRODUCT($E$103:E185)</f>
+        <v>0.68828014595547904</v>
+      </c>
+      <c r="G186" s="2">
         <v>67311</v>
       </c>
-      <c r="E186" s="3">
+      <c r="H186" s="3">
         <v>8.6427600000000009</v>
       </c>
-      <c r="F186" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G186" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I186" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J186" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>84</v>
       </c>
@@ -4871,20 +7121,32 @@
       <c r="C187" s="3">
         <v>5.16E-2</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="3">
+        <f t="shared" si="4"/>
+        <v>10.851276951469654</v>
+      </c>
+      <c r="E187" s="3">
+        <f t="shared" si="5"/>
+        <v>0.94840000000000002</v>
+      </c>
+      <c r="F187" s="9">
+        <f>PRODUCT($E$103:E186)</f>
+        <v>0.65733507059332075</v>
+      </c>
+      <c r="G187" s="2">
         <v>64069</v>
       </c>
-      <c r="E187" s="3">
+      <c r="H187" s="3">
         <v>8.0256600000000002</v>
       </c>
-      <c r="F187" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G187" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I187" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J187" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>85</v>
       </c>
@@ -4894,20 +7156,32 @@
       <c r="C188" s="3">
         <v>5.9310000000000002E-2</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="3">
+        <f t="shared" si="4"/>
+        <v>10.990533204832772</v>
+      </c>
+      <c r="E188" s="3">
+        <f t="shared" si="5"/>
+        <v>0.94069000000000003</v>
+      </c>
+      <c r="F188" s="9">
+        <f>PRODUCT($E$103:E187)</f>
+        <v>0.6234165809507054</v>
+      </c>
+      <c r="G188" s="2">
         <v>60525</v>
       </c>
-      <c r="E188" s="3">
+      <c r="H188" s="3">
         <v>7.4346699999999997</v>
       </c>
-      <c r="F188" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G188" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I188" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J188" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>86</v>
       </c>
@@ -4917,20 +7191,32 @@
       <c r="C189" s="3">
         <v>6.8229999999999999E-2</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="3">
+        <f t="shared" si="4"/>
+        <v>11.130639629809469</v>
+      </c>
+      <c r="E189" s="3">
+        <f t="shared" si="5"/>
+        <v>0.93176999999999999</v>
+      </c>
+      <c r="F189" s="9">
+        <f>PRODUCT($E$103:E188)</f>
+        <v>0.58644174353451906</v>
+      </c>
+      <c r="G189" s="2">
         <v>56676</v>
       </c>
-      <c r="E189" s="3">
+      <c r="H189" s="3">
         <v>6.8713800000000003</v>
       </c>
-      <c r="F189" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G189" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I189" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J189" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>87</v>
       </c>
@@ -4940,20 +7226,32 @@
       <c r="C190" s="3">
         <v>7.8460000000000002E-2</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="3">
+        <f t="shared" si="4"/>
+        <v>11.270344219763544</v>
+      </c>
+      <c r="E190" s="3">
+        <f t="shared" si="5"/>
+        <v>0.92154000000000003</v>
+      </c>
+      <c r="F190" s="9">
+        <f>PRODUCT($E$103:E189)</f>
+        <v>0.54642882337315879</v>
+      </c>
+      <c r="G190" s="2">
         <v>52531</v>
       </c>
-      <c r="E190" s="3">
+      <c r="H190" s="3">
         <v>6.3373799999999996</v>
       </c>
-      <c r="F190" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G190" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I190" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J190" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>88</v>
       </c>
@@ -4963,20 +7261,32 @@
       <c r="C191" s="3">
         <v>9.0260000000000007E-2</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="3">
+        <f t="shared" si="4"/>
+        <v>11.410449673380992</v>
+      </c>
+      <c r="E191" s="3">
+        <f t="shared" si="5"/>
+        <v>0.90973999999999999</v>
+      </c>
+      <c r="F191" s="9">
+        <f>PRODUCT($E$103:E190)</f>
+        <v>0.50355601789130078</v>
+      </c>
+      <c r="G191" s="2">
         <v>48112</v>
       </c>
-      <c r="E191" s="3">
+      <c r="H191" s="3">
         <v>5.8338000000000001</v>
       </c>
-      <c r="F191" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G191" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I191" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J191" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>89</v>
       </c>
@@ -4986,20 +7296,32 @@
       <c r="C192" s="3">
         <v>0.10363</v>
       </c>
-      <c r="D192" s="2">
+      <c r="D192" s="3">
+        <f t="shared" si="4"/>
+        <v>11.548582142178264</v>
+      </c>
+      <c r="E192" s="3">
+        <f t="shared" si="5"/>
+        <v>0.89637</v>
+      </c>
+      <c r="F192" s="9">
+        <f>PRODUCT($E$103:E191)</f>
+        <v>0.45810505171643195</v>
+      </c>
+      <c r="G192" s="2">
         <v>43462</v>
       </c>
-      <c r="E192" s="3">
+      <c r="H192" s="3">
         <v>5.3623700000000003</v>
       </c>
-      <c r="F192" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G192" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I192" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J192" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>90</v>
       </c>
@@ -5009,20 +7331,32 @@
       <c r="C193" s="3">
         <v>0.11878</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="3">
+        <f t="shared" si="4"/>
+        <v>11.685028321569851</v>
+      </c>
+      <c r="E193" s="3">
+        <f t="shared" si="5"/>
+        <v>0.88122</v>
+      </c>
+      <c r="F193" s="9">
+        <f>PRODUCT($E$103:E192)</f>
+        <v>0.41063162520705809</v>
+      </c>
+      <c r="G193" s="2">
         <v>38643</v>
       </c>
-      <c r="E193" s="3">
+      <c r="H193" s="3">
         <v>4.9239800000000002</v>
       </c>
-      <c r="F193" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G193" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I193" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J193" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>91</v>
       </c>
@@ -5032,20 +7366,32 @@
       <c r="C194" s="3">
         <v>0.13594000000000001</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D194" s="3">
+        <f t="shared" si="4"/>
+        <v>11.819968890900629</v>
+      </c>
+      <c r="E194" s="3">
+        <f t="shared" si="5"/>
+        <v>0.86406000000000005</v>
+      </c>
+      <c r="F194" s="9">
+        <f>PRODUCT($E$103:E193)</f>
+        <v>0.36185680076496374</v>
+      </c>
+      <c r="G194" s="2">
         <v>33737</v>
       </c>
-      <c r="E194" s="3">
+      <c r="H194" s="3">
         <v>4.5198299999999998</v>
       </c>
-      <c r="F194" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G194" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I194" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J194" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>92</v>
       </c>
@@ -5055,20 +7401,32 @@
       <c r="C195" s="3">
         <v>0.15540999999999999</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="3">
+        <f t="shared" ref="D195:D203" si="6">LN(10^6*C195)</f>
+        <v>11.953822064909657</v>
+      </c>
+      <c r="E195" s="3">
+        <f t="shared" si="5"/>
+        <v>0.84458999999999995</v>
+      </c>
+      <c r="F195" s="9">
+        <f>PRODUCT($E$103:E194)</f>
+        <v>0.3126659872689746</v>
+      </c>
+      <c r="G195" s="2">
         <v>28838</v>
       </c>
-      <c r="E195" s="3">
+      <c r="H195" s="3">
         <v>4.1519300000000001</v>
       </c>
-      <c r="F195" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G195" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I195" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J195" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>93</v>
       </c>
@@ -5078,20 +7436,32 @@
       <c r="C196" s="3">
         <v>0.17695</v>
       </c>
-      <c r="D196" s="2">
+      <c r="D196" s="3">
+        <f t="shared" si="6"/>
+        <v>12.08362248577361</v>
+      </c>
+      <c r="E196" s="3">
+        <f t="shared" ref="E196:E203" si="7">1-C196</f>
+        <v>0.82305000000000006</v>
+      </c>
+      <c r="F196" s="9">
+        <f>PRODUCT($E$103:E195)</f>
+        <v>0.26407456618750325</v>
+      </c>
+      <c r="G196" s="2">
         <v>24059</v>
       </c>
-      <c r="E196" s="3">
+      <c r="H196" s="3">
         <v>3.8239100000000001</v>
       </c>
-      <c r="F196" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G196" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I196" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J196" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>94</v>
       </c>
@@ -5101,20 +7471,32 @@
       <c r="C197" s="3">
         <v>0.19972999999999999</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="3">
+        <f t="shared" si="6"/>
+        <v>12.204721733459218</v>
+      </c>
+      <c r="E197" s="3">
+        <f t="shared" si="7"/>
+        <v>0.80027000000000004</v>
+      </c>
+      <c r="F197" s="9">
+        <f>PRODUCT($E$103:E196)</f>
+        <v>0.21734657170062457</v>
+      </c>
+      <c r="G197" s="2">
         <v>19524</v>
       </c>
-      <c r="E197" s="3">
+      <c r="H197" s="3">
         <v>3.5390899999999998</v>
       </c>
-      <c r="F197" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G197" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I197" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J197" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>95</v>
       </c>
@@ -5124,20 +7506,32 @@
       <c r="C198" s="3">
         <v>0.21648999999999999</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="3">
+        <f t="shared" si="6"/>
+        <v>12.285299635981476</v>
+      </c>
+      <c r="E198" s="3">
+        <f t="shared" si="7"/>
+        <v>0.78351000000000004</v>
+      </c>
+      <c r="F198" s="9">
+        <f>PRODUCT($E$103:E197)</f>
+        <v>0.17393594093485884</v>
+      </c>
+      <c r="G198" s="2">
         <v>15464</v>
       </c>
-      <c r="E198" s="3">
+      <c r="H198" s="3">
         <v>3.29989</v>
       </c>
-      <c r="F198" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G198" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I198" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J198" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>96</v>
       </c>
@@ -5147,20 +7541,32 @@
       <c r="C199" s="3">
         <v>0.23935000000000001</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="3">
+        <f t="shared" si="6"/>
+        <v>12.385682194820655</v>
+      </c>
+      <c r="E199" s="3">
+        <f t="shared" si="7"/>
+        <v>0.76065000000000005</v>
+      </c>
+      <c r="F199" s="9">
+        <f>PRODUCT($E$103:E198)</f>
+        <v>0.13628054908187126</v>
+      </c>
+      <c r="G199" s="2">
         <v>11942</v>
       </c>
-      <c r="E199" s="3">
+      <c r="H199" s="3">
         <v>3.0769899999999999</v>
       </c>
-      <c r="F199" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G199" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I199" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>97</v>
       </c>
@@ -5170,20 +7576,32 @@
       <c r="C200" s="3">
         <v>0.25461</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D200" s="3">
+        <f t="shared" si="6"/>
+        <v>12.447488241631833</v>
+      </c>
+      <c r="E200" s="3">
+        <f t="shared" si="7"/>
+        <v>0.74539</v>
+      </c>
+      <c r="F200" s="9">
+        <f>PRODUCT($E$103:E199)</f>
+        <v>0.10366179965912538</v>
+      </c>
+      <c r="G200" s="2">
         <v>8988</v>
       </c>
-      <c r="E200" s="3">
+      <c r="H200" s="3">
         <v>2.8931900000000002</v>
       </c>
-      <c r="F200" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G200" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I200" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J200" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>98</v>
       </c>
@@ -5193,20 +7611,32 @@
       <c r="C201" s="3">
         <v>0.27356999999999998</v>
       </c>
-      <c r="D201" s="2">
+      <c r="D201" s="3">
+        <f t="shared" si="6"/>
+        <v>12.519312809595821</v>
+      </c>
+      <c r="E201" s="3">
+        <f t="shared" si="7"/>
+        <v>0.72643000000000002</v>
+      </c>
+      <c r="F201" s="9">
+        <f>PRODUCT($E$103:E200)</f>
+        <v>7.7268468847915467E-2</v>
+      </c>
+      <c r="G201" s="2">
         <v>6619</v>
       </c>
-      <c r="E201" s="3">
+      <c r="H201" s="3">
         <v>2.7182599999999999</v>
       </c>
-      <c r="F201" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G201" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I201" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J201" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>99</v>
       </c>
@@ -5216,20 +7646,32 @@
       <c r="C202" s="3">
         <v>0.2923</v>
       </c>
-      <c r="D202" s="2">
+      <c r="D202" s="3">
+        <f t="shared" si="6"/>
+        <v>12.585535951099338</v>
+      </c>
+      <c r="E202" s="3">
+        <f t="shared" si="7"/>
+        <v>0.7077</v>
+      </c>
+      <c r="F202" s="9">
+        <f>PRODUCT($E$103:E201)</f>
+        <v>5.6130133825191234E-2</v>
+      </c>
+      <c r="G202" s="2">
         <v>4744</v>
       </c>
-      <c r="E202" s="3">
+      <c r="H202" s="3">
         <v>2.5627499999999999</v>
       </c>
-      <c r="F202" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G202" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I202" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>100</v>
       </c>
@@ -5239,21 +7681,34 @@
       <c r="C203" s="3">
         <v>0.30803000000000003</v>
       </c>
-      <c r="D203" s="2">
+      <c r="D203" s="3">
+        <f t="shared" si="6"/>
+        <v>12.637952459809789</v>
+      </c>
+      <c r="E203" s="3">
+        <f t="shared" si="7"/>
+        <v>0.69196999999999997</v>
+      </c>
+      <c r="F203" s="9">
+        <f>PRODUCT($E$103:E202)</f>
+        <v>3.9723295708087837E-2</v>
+      </c>
+      <c r="G203" s="2">
         <v>9641</v>
       </c>
-      <c r="E203" s="3">
+      <c r="H203" s="3">
         <v>2.4270399999999999</v>
       </c>
-      <c r="F203" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G203" s="6" t="s">
+      <c r="I203" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J203" s="7" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>